--- a/data/donnees_carte_amidomar.xlsx
+++ b/data/donnees_carte_amidomar.xlsx
@@ -866,7 +866,8 @@
       <c r="E13" s="2" t="n"/>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Corrigé dans index.html le 21/09/2026 (endpoints natura-habitat et natura-oiseaux, champ sitename, délai porté à 8 s) et testé en réel sur 5 points (Port-Cros, Lavezzi, golfe du Morbihan, Beauduc, large de Quiberon). Non testé sur Brest. Le nom de site est bien identifié, mais les zones Natura 2000 restent affichées en image (voir lignes d'affichage).</t>
+          <t>Corrigé dans index.html le 21/09/2026 (endpoints natura-habitat et natura-oiseaux, champ sitename, délai porté à 8 s) et testé en réel sur 5 points (Port-Cros, Lavezzi, golfe du Morbihan, Beauduc, large de Quiberon). Non testé sur Brest. Le nom de site est bien identifié, mais les zones Natura 2000 restent affichées en image (voir lignes d'affichage).
+Repli branché le 21/09/2026 (v1.9) : si l'API Carto échoue, la carte interroge le WFS de la Géoplateforme (patrinat_sic, patrinat_zps). Test réel : l'API Carto a dépassé 8 s sur 2 requêtes Natura 2000 à Port-Cros, le repli a rendu « Rade d'Hyères » et « Iles d'Hyères ».</t>
         </is>
       </c>
     </row>
@@ -889,14 +890,13 @@
       <c r="D14" s="3" t="inlineStr"/>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Ce qui ne va pas : le clic fonctionne, mais rien n'est renvoyé en mer sur les points testés.
-Ce qu'il faut : une source de clic pour les ZNIEFF marines.</t>
+          <t>Ce qui ne va pas : l'API Carto ne renvoie rien en mer pour les ZNIEFF. Un repli sur le WFS de la Géoplateforme (couches marines znieff1_mer et znieff2_mer) est branché depuis le 21/09/2026 ; il n'est confirmé que sur un point marin (Île Riou), pas sur la carte publiée.
+Ce qu'il faut : tester sur d'autres ZNIEFF marines connues une fois la version en ligne.</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>Tester le WFS de la Géoplateforme (patrinat_znieff1 et patrinat_znieff2) sur un point en mer, ou charger le jeu INPN complet (terrestre et marin) : https://www.data.gouv.fr/datasets/inpn-donnees-du-programme-znieff
-Piste testée le 21/09/2026 : le WFS de la Géoplateforme (couches patrinat_znieff1_mer et patrinat_znieff2_mer, filtre INTERSECTS sur le point cliqué) répond en mer ; voir les lignes d'affichage. Non branché dans la carte.</t>
+          <t>Repli WFS (v1.9) : patrinat_znieff1_mer et patrinat_znieff2_mer, filtre INTERSECTS sur le point cliqué. Test réel du 21/09/2026 : Île Riou → « ILE RIOU, ILOTS CONGLUÉ ET IMPÉRIAUX » (l'API Carto avait dépassé 8 s). Alternative : charger le jeu INPN complet : https://www.data.gouv.fr/datasets/inpn-donnees-du-programme-znieff</t>
         </is>
       </c>
     </row>
@@ -1138,7 +1138,7 @@
       <c r="D22" s="3" t="inlineStr"/>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>Ce qui ne va pas : la zone s'affiche comme une image, sans identification au clic. Le nom Patrinat_APB et les tuiles sont confirmés (test du 21/09/2026 : tuiles reçues sur 6 des 7 sites essayés, aucune à Hyères sur la tuile testée) ; l'affichage dans la carte elle-même n'a pas été vérifié à l'œil.
+          <t>Ce qui ne va pas : la zone s'affiche comme une image, sans identification au clic. Le nom Patrinat_APB et les tuiles sont confirmés (test du 21/09/2026 : tuiles reçues sur 6 des 7 sites essayés, aucune à Hyères sur la tuile testée) ; les APB s'affichent en orange vif (255, 128, 0), en fins contours et petits aplats, peu visibles quand on est dézoomé, et de couleur proche de celle des aires marines protégées ; des polygones orange sont visibles au Morbihan (zoom 11) sur la carte publiée, très probablement les APB (non confirmé en masquant la couche).
 Ce qu'il faut : ouvrir la carte publiée et vérifier le rendu, puis chercher les contours en données.</t>
         </is>
       </c>

--- a/data/donnees_carte_amidomar.xlsx
+++ b/data/donnees_carte_amidomar.xlsx
@@ -1120,31 +1120,31 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="inlineStr">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>Arrêtés de protection de biotope (APB)</t>
         </is>
       </c>
-      <c r="B22" s="3" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>IGN / INPN, Patrinat_APB</t>
         </is>
       </c>
-      <c r="C22" s="3" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
         <is>
           <t>WMTS, tuiles PNG raster</t>
         </is>
       </c>
-      <c r="D22" s="3" t="inlineStr"/>
-      <c r="E22" s="3" t="inlineStr">
-        <is>
-          <t>Ce qui ne va pas : la zone s'affiche comme une image, sans identification au clic. Le nom Patrinat_APB et les tuiles sont confirmés (test du 21/09/2026 : tuiles reçues sur 6 des 7 sites essayés, aucune à Hyères sur la tuile testée) ; les APB s'affichent en orange vif (255, 128, 0), en fins contours et petits aplats, peu visibles quand on est dézoomé, et de couleur proche de celle des aires marines protégées ; des polygones orange sont visibles au Morbihan (zoom 11) sur la carte publiée, très probablement les APB (non confirmé en masquant la couche).
-Ce qu'il faut : ouvrir la carte publiée et vérifier le rendu, puis chercher les contours en données.</t>
-        </is>
-      </c>
-      <c r="F22" s="3" t="inlineStr">
-        <is>
-          <t>Contours en données : couche patrinat_apb confirmée dans le WFS de la Géoplateforme (document de capacités interrogé le 21/09/2026 ; requête de données non testée) : https://data.geopf.fr/wfs?REQUEST=GetCapabilities&amp;SERVICE=WFS&amp;VERSION=2.0.0</t>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>données fonctionnelles</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="n"/>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>Affichage : couche patrinat_apb confirmée en WFS et en WMTS le 21/09/2026 ; polygones vus au Morbihan (zoom 11), couleur de légende orange alignée sur les tuiles.
+Au clic (v2.0, 22/09/2026) : couche patrinat_apb:apb, champ nom_site, filtre INTERSECTS. Testé en direct sur l'APB « Ile Dumet et ses abords » (centre du polygone, pas un sommet) : nom renvoyé en ~480 ms. Traité comme une interdiction bloquante, prioritaire sur Natura 2000/ZNIEFF (popup rouge, pas de coordonnées), vérifiée avant tout affichage (délai 4 s, défaut non bloquant). Reste à tester : un clic réel dans un APB sur la carte publiée.</t>
         </is>
       </c>
     </row>

--- a/data/donnees_carte_amidomar.xlsx
+++ b/data/donnees_carte_amidomar.xlsx
@@ -479,7 +479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1029,59 +1029,89 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Bathymétrie</t>
+          <t>Profondeur au point (colonne d'eau à marée haute)</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Aucune</t>
+          <t>EMODnet Bathymetry, API depth_sample (grille européenne intégrant les levés du Shom)</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>JSON (REST), maille d'environ 115 m</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr"/>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>Ce qui ne va pas : aucune profondeur disponible, l'usager la saisit à la main, donc le rayon d'évitage n'est qu'indicatif.
-Ce qu'il faut : un fichier de profondeurs marines lisible au point cliqué.</t>
+          <t>Ce qui ne va pas : branché en v2.6 (25/09/2026) et testé sur l'API réelle, mais le clic complet sur la carte publiée avec l'API réelle reste à vérifier ; la maille d'environ 115 m donne un fond moyen, peu fidèle près des roches et des chenaux.
+Ce qu'il faut : un test en conditions réelles sur la carte publiée, puis, si besoin, une bathymétrie plus fine sur les zones pilotes (MNT côtiers du Shom à 5-20 m).</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>MNT de façade du Shom (projet Homonim), gratuits en licence ouverte, résolution 0,001° soit environ 111 m, en formats ASC, GLZ, BAG, GRD, à télécharger par zone. Ce sont des grilles à convertir avant usage sur la carte, et 111 m est grossier près du rivage (mon évaluation).
-Atlantique, Manche, mer du Nord : https://diffusion.shom.fr/donnees/bathymerie/mnt-facade-atl-homonim.html
-Golfe du Lion - Côte d'Azur : https://diffusion.shom.fr/mnt-facade-gdl-ca-homonim.html
-Corse : https://diffusion.shom.fr/mnt-facade-atl-homonim_1.html</t>
+          <t>API testée le 25/09/2026 depuis le site publié : CORS accepté, 60 à 370 ms ; Quiberon −12,35 m, Brest −23,6 m, Saint-Malo −1,86 m. https://rest.emodnet-bathymetry.eu/depth_sample?geom=POINT(-2.970485 47.510572)
+Écartés : WMS « MNT » du Shom non interrogeable au point (LayerNotQueryable), export image/x-bil incohérent (tests du 25/09/2026).
+Plus fin (non testé) : MNT côtiers du Shom à 5-20 m (Morbihan, Pertuis, Arcachon, Île de Ré, Gironde…) visibles dans le WMS INSPIRE, à télécharger et convertir : https://diffusion.shom.fr/donnees/bathymerie/mnt-bathymetriques.html
+MNT de façade Homonim (111 m, Licence Ouverte) : https://www.data.gouv.fr/datasets/mnt-bathymetrique-de-facade-atlantique-projet-homonim-1</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
+          <t>Hauteur de marée haute (colonne d'eau à marée haute)</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>data/ram-ports.json, extrait du Shom, Références Altimétriques Maritimes (WFS RAM_BDD_WLD_WGS84G_WFS:ram_3857)</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>JSON, 214 ports (métropole)</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="n"/>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>Ce qui ne va pas : valeur fixe par port (vives-eaux moyennes, coefficient 95), pas la marée du jour ; port choisi à vol d'oiseau, parfois de l'autre côté d'une pointe ; 15 ports sans valeurs exploitables écartés ; extraction du 25/09/2026 à rafraîchir si le Shom publie une nouvelle édition.
+Ce qu'il faut : garder la table à jour ; pour la marée du jour, un abonnement aux API de prédiction du Shom (payant) avec un petit serveur intermédiaire.</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>Source ouverte (Licence Ouverte, citer « Shom, 2025 ») : https://www.data.gouv.fr/datasets/references-altimetriques-maritimes — WFS interrogé le 25/09/2026 (446 sites, 229 en métropole, sommes de contrôle notées dans TESTS_FONCTIONNELS.md §5/9quinquies).
+API marée du Shom (payantes, clé) : https://diffusion.shom.fr/api-shom.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
           <t>Vent, courant, nature du fond</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>Aucune</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="C21" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D20" s="3" t="inlineStr"/>
-      <c r="E20" s="3" t="inlineStr">
+      <c r="D21" s="3" t="inlineStr"/>
+      <c r="E21" s="3" t="inlineStr">
         <is>
           <t>Ce qui ne va pas : le calcul du rayon d'évitage ignore le vent, le courant et le type de fond, qui changent la zone réellement balayée par le bateau.
 Ce qu'il faut : ces trois données.</t>
         </is>
       </c>
-      <c r="F20" s="3" t="inlineStr">
+      <c r="F21" s="3" t="inlineStr">
         <is>
           <t>Nature du fond : Natures de fond au 1/50 000 (Shom), 47 cartes, shapefile et GML, WMS/WMTS/WFS, gratuit, version 2025 : https://diffusion.shom.fr/donnees/sedimentologie/natures-de-fond.html
 Courants : la page Shom des courants de marée 2D était inaccessible au test, et l'API Shom ne liste ni courants ni vent (marées payantes) : https://diffusion.shom.fr/services-numeriques/api-shom.html
@@ -1090,142 +1120,142 @@
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="3" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
         <is>
           <t>Réserves naturelles nationales</t>
         </is>
       </c>
-      <c r="B21" s="3" t="inlineStr">
+      <c r="B22" s="3" t="inlineStr">
         <is>
           <t>Patrinat_RNN (Géoplateforme)</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr">
+      <c r="C22" s="3" t="inlineStr">
         <is>
           <t>Non testé</t>
         </is>
       </c>
-      <c r="D21" s="3" t="inlineStr"/>
-      <c r="E21" s="3" t="inlineStr">
+      <c r="D22" s="3" t="inlineStr"/>
+      <c r="E22" s="3" t="inlineStr">
         <is>
           <t>Ce qui ne va pas : la couche existe mais n'est pas sur la carte, alors que la note la donne « en service ».
 Ce qu'il faut : l'ajouter et la tester.</t>
         </is>
       </c>
-      <c r="F21" s="3" t="inlineStr">
+      <c r="F22" s="3" t="inlineStr">
         <is>
           <t>Couche patrinat_rnn confirmée dans le document de capacités WFS de la Géoplateforme (21/09/2026) : https://data.geopf.fr/wfs?REQUEST=GetCapabilities&amp;SERVICE=WFS&amp;VERSION=2.0.0</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>Arrêtés de protection de biotope (APB)</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>IGN / INPN, Patrinat_APB</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
         <is>
           <t>WMTS, tuiles PNG raster</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>données fonctionnelles</t>
         </is>
       </c>
-      <c r="E22" s="2" t="n"/>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="E23" s="2" t="n"/>
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>Affichage : couche patrinat_apb confirmée en WFS et en WMTS le 21/09/2026 ; polygones vus au Morbihan (zoom 11), couleur de légende orange alignée sur les tuiles.
 Au clic (v2.0, 22/09/2026) : couche patrinat_apb:apb, champ nom_site, filtre INTERSECTS. Testé en direct sur l'APB « Ile Dumet et ses abords » (centre du polygone, pas un sommet) : nom renvoyé en ~480 ms. Traité comme une interdiction bloquante, prioritaire sur Natura 2000/ZNIEFF (popup rouge, pas de coordonnées), vérifiée avant tout affichage (délai 4 s, défaut non bloquant). Reste à tester : un clic réel dans un APB sur la carte publiée.</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="3" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
         <is>
           <t>Autres zonages (Ramsar, RNR, Conservatoire du littoral)</t>
         </is>
       </c>
-      <c r="B23" s="3" t="inlineStr">
+      <c r="B24" s="3" t="inlineStr">
         <is>
           <t>Patrinat_RAMSAR, Patrinat_RNR, CONSERVATOIRE_LITTORAL.PERIMETRES</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr">
+      <c r="C24" s="3" t="inlineStr">
         <is>
           <t>Non testé</t>
         </is>
       </c>
-      <c r="D23" s="3" t="inlineStr"/>
-      <c r="E23" s="3" t="inlineStr">
+      <c r="D24" s="3" t="inlineStr"/>
+      <c r="E24" s="3" t="inlineStr">
         <is>
           <t>Ce qui ne va pas : couches existantes mais absentes de la carte.
 Ce qu'il faut : décider si le besoin métier justifie de les ajouter, puis vérifier le rendu.</t>
         </is>
       </c>
-      <c r="F23" s="3" t="inlineStr">
+      <c r="F24" s="3" t="inlineStr">
         <is>
           <t>WFS Géoplateforme : patrinat_ramsar et CONSERVATOIRE_LITTORAL.PERIMETRES sont listées ; patrinat_rnr y figure aussi (noms confirmés le 21/09/2026 ; requêtes de données non testées) : https://data.geopf.fr/wfs?REQUEST=GetCapabilities&amp;SERVICE=WFS&amp;VERSION=2.0.0
 Espaces protégés du Conservatoire du littoral (titre repéré, non ouvert) : https://www.data.gouv.fr/datasets/site-des-espaces-proteges-du-conservatoire-du-littoral</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="3" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
         <is>
           <t>Zones de baignade et zones réglementaires</t>
         </is>
       </c>
-      <c r="B24" s="3" t="inlineStr">
+      <c r="B25" s="3" t="inlineStr">
         <is>
           <t>Aucune</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr">
+      <c r="C25" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D24" s="3" t="n"/>
-      <c r="E24" s="3" t="inlineStr">
+      <c r="D25" s="3" t="n"/>
+      <c r="E25" s="3" t="inlineStr">
         <is>
           <t>Ce qui ne va pas : ligne « à venir » dans la légende, grisée et non sélectionnable. Aucune source n'est identifiée pour représenter ces zones ni les reconnaître au clic.
 Ce qu'il faut : identifier une source pour chacune des deux.</t>
         </is>
       </c>
-      <c r="F24" s="3" t="inlineStr">
+      <c r="F25" s="3" t="inlineStr">
         <is>
           <t>Aucune source confirmée. Pistes non vérifiées : données de baignade publiées par les communes ou les ARS, arrêtés préfectoraux à demander aux DDTM/DM.</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="5" t="n"/>
-    </row>
     <row r="26">
-      <c r="A26" s="5" t="inlineStr">
-        <is>
-          <t>Légende : vert = données fonctionnelles ; jaune = données simulées ; sans couleur = à compléter.</t>
-        </is>
-      </c>
+      <c r="A26" s="5" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>Méthode (21/09/2026) : les fiches de jeux de données ont été ouvertes et lues ; les services WMS/WFS et les fichiers n'ont pas été interrogés ni téléchargés. « Titre repéré, non ouvert » = trouvé par recherche seulement.</t>
+          <t>Légende : vert = données fonctionnelles ; jaune = données simulées ; sans couleur = à compléter.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>Méthode (21/09/2026) : les fiches de jeux de données ont été ouvertes et lues ; les services WMS/WFS et les fichiers n'ont pas été interrogés ni téléchargés. « Titre repéré, non ouvert » = trouvé par recherche seulement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
         <is>
           <t>Le document de capacités WFS et WMTS de la Géoplateforme a été interrogé dans un navigateur le 21/09/2026 : les noms de couches patrinat_* cités ici y figurent. Aucune requête de données (GetFeature) n'a encore été testée.</t>
         </is>
@@ -1242,7 +1272,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C44"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -1831,7 +1861,7 @@
     <row r="35">
       <c r="A35" s="7" t="inlineStr">
         <is>
-          <t>Bathymétrie</t>
+          <t>Profondeur au point (colonne d'eau à marée haute)</t>
         </is>
       </c>
       <c r="B35" s="8" t="inlineStr">
@@ -1848,7 +1878,7 @@
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t>Bathymétrie</t>
+          <t>Profondeur au point (colonne d'eau à marée haute)</t>
         </is>
       </c>
       <c r="B36" s="8" t="inlineStr">
@@ -1865,7 +1895,7 @@
     <row r="37">
       <c r="A37" s="7" t="inlineStr">
         <is>
-          <t>Bathymétrie</t>
+          <t>Profondeur au point (colonne d'eau à marée haute)</t>
         </is>
       </c>
       <c r="B37" s="8" t="inlineStr">
@@ -1995,6 +2025,91 @@
       <c r="C44" s="7" t="inlineStr">
         <is>
           <t>Repéré en recherche, non ouvert</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="7" t="inlineStr">
+        <is>
+          <t>Profondeur au point (colonne d'eau à marée haute)</t>
+        </is>
+      </c>
+      <c r="B45" s="8" t="inlineStr">
+        <is>
+          <t>https://www.data.gouv.fr/datasets/mnt-bathymetrique-de-facade-atlantique-projet-homonim-1</t>
+        </is>
+      </c>
+      <c r="C45" s="7" t="inlineStr">
+        <is>
+          <t>Page ouverte le 25/09/2026 (licence, résolution et ressources lues ; WMS non interrogé)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="7" t="inlineStr">
+        <is>
+          <t>Profondeur au point (colonne d'eau à marée haute)</t>
+        </is>
+      </c>
+      <c r="B46" s="8" t="inlineStr">
+        <is>
+          <t>https://diffusion.shom.fr/api-shom.html</t>
+        </is>
+      </c>
+      <c r="C46" s="7" t="inlineStr">
+        <is>
+          <t>Page ouverte le 25/09/2026 (API marée payantes avec clé)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="7" t="inlineStr">
+        <is>
+          <t>Profondeur au point (colonne d'eau à marée haute)</t>
+        </is>
+      </c>
+      <c r="B47" s="8" t="inlineStr">
+        <is>
+          <t>https://services.data.shom.fr/support/en/services/spm</t>
+        </is>
+      </c>
+      <c r="C47" s="7" t="inlineStr">
+        <is>
+          <t>Page ouverte le 25/09/2026 (SPM/SAPM : clé d'abonnement obligatoire)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="7" t="inlineStr">
+        <is>
+          <t>Profondeur au point (colonne d'eau à marée haute)</t>
+        </is>
+      </c>
+      <c r="B48" s="8" t="inlineStr">
+        <is>
+          <t>https://rest.emodnet-bathymetry.eu/depth_sample?geom=POINT(-2.970485 47.510572)</t>
+        </is>
+      </c>
+      <c r="C48" s="7" t="inlineStr">
+        <is>
+          <t>API interrogée le 25/09/2026 depuis le site publié (réponse JSON, CORS OK)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="7" t="inlineStr">
+        <is>
+          <t>Hauteur de marée haute (colonne d'eau à marée haute)</t>
+        </is>
+      </c>
+      <c r="B49" s="8" t="inlineStr">
+        <is>
+          <t>https://www.data.gouv.fr/datasets/references-altimetriques-maritimes</t>
+        </is>
+      </c>
+      <c r="C49" s="7" t="inlineStr">
+        <is>
+          <t>Fiche lue le 25/09/2026 (licence, ressources) ; WFS du Shom interrogé le même jour</t>
         </is>
       </c>
     </row>
@@ -2043,6 +2158,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B42" r:id="rId41"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B43" r:id="rId42"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B49" r:id="rId48"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/donnees_carte_amidomar.xlsx
+++ b/data/donnees_carte_amidomar.xlsx
@@ -479,7 +479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -928,33 +928,62 @@
 Charente-Maritime (DDTM 17) : shapefile, WMS/WFS, mis à jour en 2024 : https://www.data.gouv.fr/datasets/zones-de-mouillages-et-dequipements-legers-zmel-en-charente-maritime
 Finistère (DDTM 29, jeu archivé, donnée d'avril 2025) : https://www.data.gouv.fr/datasets/mouillages-groupes-du-finistere-1/
 Morbihan (titre repéré, non ouvert) : https://www.data.gouv.fr/datasets/zones-de-mouillage-et-dequipements-legers-zmel-departement-du-morbihan-1
-Vue nationale : 260 ZMEL dans 209 communes sur GéoLittoral, sans téléchargement annoncé ; demande possible à geolittoral@cerema.fr : https://www.geolittoral.developpement-durable.gouv.fr/zones-de-mouillage-et-d-equipements-legers-a1757.html?lang=fr</t>
+Vue nationale : 260 ZMEL dans 209 communes sur GéoLittoral, sans téléchargement annoncé ; demande possible à geolittoral@cerema.fr : https://www.geolittoral.developpement-durable.gouv.fr/zones-de-mouillage-et-d-equipements-legers-a1757.html?lang=fr
+25/09/2026 : Nicolas a fourni un shapefile Cerema/CACEM (647 ZMEL, France entière) — converti dans data/zmel-reel.geojson (voir ligne ci-dessous), mais pas encore branché ici.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
+          <t>ZMEL (données réelles converties, non branchées)</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>data/zmel-reel.geojson — shapefile Cerema/CACEM fourni par Nicolas (ZMEL_18_09_2026), converti</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>GeoJSON, 647 polygones/multipolygones, France entière + Antilles, reprojeté Lambert-93 → WGS84</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="n"/>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>Converti et vérifié géométriquement (bbox plausible, 0 entité perdue) le 25/09/2026, mais PAS ENCORE branché sur la carte (data/zmel.geojson, fictif, reste la source active). Schéma d'attributs différent de celui attendu par modaleZmel() : nb_postes_ est un total agrégé en texte (pas de nombre par navire simple), pas de champ e-mail/contact. Lien url_v2 (fiches Légicem) injoignable depuis l'extérieur : domaine legicem.metier.e2.rie.gouv.fr sur le RIE (réseau interministériel de l'État), échec de connexion confirmé le 25/09/2026 — inutilisable pour récupérer un contact, y compris pour le public. Champ redev_an_z/redev_an_p (redevance) présent mais volontairement pas prévu à l'affichage public (sensible).</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>Shapefile fourni directement par Nicolas le 25/09/2026 (source Cerema/CACEM, pas encore identifiée avec certitude comme le jeu GéoLittoral national mentionné ligne ZMEL ci-dessus — à confirmer). Reste à faire pour brancher : ajouter une entrée COUCHES pointant sur ce fichier, adapter ou étendre modaleZmel() si besoin, décider du remplacement (ou non) de data/zmel.geojson.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
           <t>Cultures marines</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>data/cultures-marines.geojson</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>GeoJSON, 1 polygone fictif</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr"/>
-      <c r="E16" s="4" t="inlineStr">
+      <c r="D17" s="4" t="inlineStr"/>
+      <c r="E17" s="4" t="inlineStr">
         <is>
           <t>données simulées</t>
         </is>
       </c>
-      <c r="F16" s="4" t="inlineStr">
+      <c r="F17" s="4" t="inlineStr">
         <is>
           <t>Aucun cadastre conchylicole national trouvé : il se récupère département par département.
 Manche (DDTM 50, shapefile, WMS/WFS, 2025) : https://www.data.gouv.fr/datasets/cadastre-conchylicole-1
@@ -965,29 +994,29 @@
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
         <is>
           <t>Ports de plaisance (places, contact)</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>data/ports-plaisance.geojson</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C18" s="4" t="inlineStr">
         <is>
           <t>GeoJSON, 6 points</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr"/>
-      <c r="E17" s="4" t="inlineStr">
+      <c r="D18" s="4" t="inlineStr"/>
+      <c r="E18" s="4" t="inlineStr">
         <is>
           <t>données simulées</t>
         </is>
       </c>
-      <c r="F17" s="4" t="inlineStr">
+      <c r="F18" s="4" t="inlineStr">
         <is>
           <t>Observatoire des ports de plaisance (Ministère, GéoLittoral) : 488 ports en métropole ; la page annonce des capacités d'accueil et des certifications téléchargeables sur son portail de données (format et licence non vérifiés) : https://www.geolittoral.developpement-durable.gouv.fr/observatoire-des-ports-de-plaisance-a1733.html?lang=fr
 Caractéristiques des ports en France 2021 (PIGMA, titre repéré, non ouvert) : https://www.pigma.org/geonetwork/5a8srv/api/records/00c61236-da83-4215-ab58-b0ee88925cf4
@@ -995,29 +1024,29 @@
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>AOT existantes</t>
         </is>
       </c>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>data/aot-existantes.geojson</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t>GeoJSON, 249 points</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr"/>
-      <c r="E18" s="4" t="inlineStr">
+      <c r="D19" s="4" t="inlineStr"/>
+      <c r="E19" s="4" t="inlineStr">
         <is>
           <t>données simulées</t>
         </is>
       </c>
-      <c r="F18" s="4" t="inlineStr">
+      <c r="F19" s="4" t="inlineStr">
         <is>
           <t>Des positions réelles sont déjà publiées :
 Finistère (DDTM 29) : mouillages individuels sous AOT représentés par un cercle, shapefile, WMS/WFS, extraction ADOC du 28/05/2026, mis à jour le 29/05/2026. Les champs (longueur, statut) ne sont pas documentés sur la page : https://www.data.gouv.fr/datasets/mouillages-individuels-du-finistere-1
@@ -1026,30 +1055,30 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="3" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>Profondeur au point (colonne d'eau à marée haute)</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B20" s="3" t="inlineStr">
         <is>
           <t>EMODnet Bathymetry, API depth_sample (grille européenne intégrant les levés du Shom)</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="C20" s="3" t="inlineStr">
         <is>
           <t>JSON (REST), maille d'environ 115 m</t>
         </is>
       </c>
-      <c r="D19" s="3" t="inlineStr"/>
-      <c r="E19" s="3" t="inlineStr">
+      <c r="D20" s="3" t="inlineStr"/>
+      <c r="E20" s="3" t="inlineStr">
         <is>
           <t>Ce qui ne va pas : branché en v2.6 (25/09/2026) et testé sur l'API réelle, mais le clic complet sur la carte publiée avec l'API réelle reste à vérifier ; la maille d'environ 115 m donne un fond moyen, peu fidèle près des roches et des chenaux.
 Ce qu'il faut : un test en conditions réelles sur la carte publiée, puis, si besoin, une bathymétrie plus fine sur les zones pilotes (MNT côtiers du Shom à 5-20 m).</t>
         </is>
       </c>
-      <c r="F19" s="3" t="inlineStr">
+      <c r="F20" s="3" t="inlineStr">
         <is>
           <t>API testée le 25/09/2026 depuis le site publié : CORS accepté, 60 à 370 ms ; Quiberon −12,35 m, Brest −23,6 m, Saint-Malo −1,86 m. https://rest.emodnet-bathymetry.eu/depth_sample?geom=POINT(-2.970485 47.510572)
 Écartés : WMS « MNT » du Shom non interrogeable au point (LayerNotQueryable), export image/x-bil incohérent (tests du 25/09/2026).
@@ -1058,60 +1087,60 @@
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>Hauteur de marée haute (colonne d'eau à marée haute)</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>data/ram-ports.json, extrait du Shom, Références Altimétriques Maritimes (WFS RAM_BDD_WLD_WGS84G_WFS:ram_3857)</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="C21" s="3" t="inlineStr">
         <is>
           <t>JSON, 214 ports (métropole)</t>
         </is>
       </c>
-      <c r="D20" s="3" t="n"/>
-      <c r="E20" s="3" t="inlineStr">
+      <c r="D21" s="3" t="n"/>
+      <c r="E21" s="3" t="inlineStr">
         <is>
           <t>Ce qui ne va pas : valeur fixe par port (vives-eaux moyennes, coefficient 95), pas la marée du jour ; port choisi à vol d'oiseau, parfois de l'autre côté d'une pointe ; 15 ports sans valeurs exploitables écartés ; extraction du 25/09/2026 à rafraîchir si le Shom publie une nouvelle édition.
 Ce qu'il faut : garder la table à jour ; pour la marée du jour, un abonnement aux API de prédiction du Shom (payant) avec un petit serveur intermédiaire.</t>
         </is>
       </c>
-      <c r="F20" s="3" t="inlineStr">
+      <c r="F21" s="3" t="inlineStr">
         <is>
           <t>Source ouverte (Licence Ouverte, citer « Shom, 2025 ») : https://www.data.gouv.fr/datasets/references-altimetriques-maritimes — WFS interrogé le 25/09/2026 (446 sites, 229 en métropole, sommes de contrôle notées dans TESTS_FONCTIONNELS.md §5/9quinquies).
 API marée du Shom (payantes, clé) : https://diffusion.shom.fr/api-shom.html</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="3" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
         <is>
           <t>Vent, courant, nature du fond</t>
         </is>
       </c>
-      <c r="B21" s="3" t="inlineStr">
+      <c r="B22" s="3" t="inlineStr">
         <is>
           <t>Aucune</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr">
+      <c r="C22" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D21" s="3" t="inlineStr"/>
-      <c r="E21" s="3" t="inlineStr">
+      <c r="D22" s="3" t="inlineStr"/>
+      <c r="E22" s="3" t="inlineStr">
         <is>
           <t>Ce qui ne va pas : le calcul du rayon d'évitage ignore le vent, le courant et le type de fond, qui changent la zone réellement balayée par le bateau.
 Ce qu'il faut : ces trois données.</t>
         </is>
       </c>
-      <c r="F21" s="3" t="inlineStr">
+      <c r="F22" s="3" t="inlineStr">
         <is>
           <t>Nature du fond : Natures de fond au 1/50 000 (Shom), 47 cartes, shapefile et GML, WMS/WMTS/WFS, gratuit, version 2025 : https://diffusion.shom.fr/donnees/sedimentologie/natures-de-fond.html
 Courants : la page Shom des courants de marée 2D était inaccessible au test, et l'API Shom ne liste ni courants ni vent (marées payantes) : https://diffusion.shom.fr/services-numeriques/api-shom.html
@@ -1120,142 +1149,142 @@
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="3" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
         <is>
           <t>Réserves naturelles nationales</t>
         </is>
       </c>
-      <c r="B22" s="3" t="inlineStr">
+      <c r="B23" s="3" t="inlineStr">
         <is>
           <t>Patrinat_RNN (Géoplateforme)</t>
         </is>
       </c>
-      <c r="C22" s="3" t="inlineStr">
+      <c r="C23" s="3" t="inlineStr">
         <is>
           <t>Non testé</t>
         </is>
       </c>
-      <c r="D22" s="3" t="inlineStr"/>
-      <c r="E22" s="3" t="inlineStr">
+      <c r="D23" s="3" t="inlineStr"/>
+      <c r="E23" s="3" t="inlineStr">
         <is>
           <t>Ce qui ne va pas : la couche existe mais n'est pas sur la carte, alors que la note la donne « en service ».
 Ce qu'il faut : l'ajouter et la tester.</t>
         </is>
       </c>
-      <c r="F22" s="3" t="inlineStr">
+      <c r="F23" s="3" t="inlineStr">
         <is>
           <t>Couche patrinat_rnn confirmée dans le document de capacités WFS de la Géoplateforme (21/09/2026) : https://data.geopf.fr/wfs?REQUEST=GetCapabilities&amp;SERVICE=WFS&amp;VERSION=2.0.0</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>Arrêtés de protection de biotope (APB)</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>IGN / INPN, Patrinat_APB</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t>WMTS, tuiles PNG raster</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>données fonctionnelles</t>
         </is>
       </c>
-      <c r="E23" s="2" t="n"/>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="E24" s="2" t="n"/>
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>Affichage : couche patrinat_apb confirmée en WFS et en WMTS le 21/09/2026 ; polygones vus au Morbihan (zoom 11), couleur de légende orange alignée sur les tuiles.
 Au clic (v2.0, 22/09/2026) : couche patrinat_apb:apb, champ nom_site, filtre INTERSECTS. Testé en direct sur l'APB « Ile Dumet et ses abords » (centre du polygone, pas un sommet) : nom renvoyé en ~480 ms. Traité comme une interdiction bloquante, prioritaire sur Natura 2000/ZNIEFF (popup rouge, pas de coordonnées), vérifiée avant tout affichage (délai 4 s, défaut non bloquant). Reste à tester : un clic réel dans un APB sur la carte publiée.</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="3" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
         <is>
           <t>Autres zonages (Ramsar, RNR, Conservatoire du littoral)</t>
         </is>
       </c>
-      <c r="B24" s="3" t="inlineStr">
+      <c r="B25" s="3" t="inlineStr">
         <is>
           <t>Patrinat_RAMSAR, Patrinat_RNR, CONSERVATOIRE_LITTORAL.PERIMETRES</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr">
+      <c r="C25" s="3" t="inlineStr">
         <is>
           <t>Non testé</t>
         </is>
       </c>
-      <c r="D24" s="3" t="inlineStr"/>
-      <c r="E24" s="3" t="inlineStr">
+      <c r="D25" s="3" t="inlineStr"/>
+      <c r="E25" s="3" t="inlineStr">
         <is>
           <t>Ce qui ne va pas : couches existantes mais absentes de la carte.
 Ce qu'il faut : décider si le besoin métier justifie de les ajouter, puis vérifier le rendu.</t>
         </is>
       </c>
-      <c r="F24" s="3" t="inlineStr">
+      <c r="F25" s="3" t="inlineStr">
         <is>
           <t>WFS Géoplateforme : patrinat_ramsar et CONSERVATOIRE_LITTORAL.PERIMETRES sont listées ; patrinat_rnr y figure aussi (noms confirmés le 21/09/2026 ; requêtes de données non testées) : https://data.geopf.fr/wfs?REQUEST=GetCapabilities&amp;SERVICE=WFS&amp;VERSION=2.0.0
 Espaces protégés du Conservatoire du littoral (titre repéré, non ouvert) : https://www.data.gouv.fr/datasets/site-des-espaces-proteges-du-conservatoire-du-littoral</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="3" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
         <is>
           <t>Zones de baignade et zones réglementaires</t>
         </is>
       </c>
-      <c r="B25" s="3" t="inlineStr">
+      <c r="B26" s="3" t="inlineStr">
         <is>
           <t>Aucune</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr">
+      <c r="C26" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D25" s="3" t="n"/>
-      <c r="E25" s="3" t="inlineStr">
+      <c r="D26" s="3" t="n"/>
+      <c r="E26" s="3" t="inlineStr">
         <is>
           <t>Ce qui ne va pas : ligne « à venir » dans la légende, grisée et non sélectionnable. Aucune source n'est identifiée pour représenter ces zones ni les reconnaître au clic.
 Ce qu'il faut : identifier une source pour chacune des deux.</t>
         </is>
       </c>
-      <c r="F25" s="3" t="inlineStr">
+      <c r="F26" s="3" t="inlineStr">
         <is>
           <t>Aucune source confirmée. Pistes non vérifiées : données de baignade publiées par les communes ou les ARS, arrêtés préfectoraux à demander aux DDTM/DM.</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="5" t="n"/>
-    </row>
     <row r="27">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>Légende : vert = données fonctionnelles ; jaune = données simulées ; sans couleur = à compléter.</t>
-        </is>
-      </c>
+      <c r="A27" s="5" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>Méthode (21/09/2026) : les fiches de jeux de données ont été ouvertes et lues ; les services WMS/WFS et les fichiers n'ont pas été interrogés ni téléchargés. « Titre repéré, non ouvert » = trouvé par recherche seulement.</t>
+          <t>Légende : vert = données fonctionnelles ; jaune = données simulées ; sans couleur = à compléter.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>Méthode (21/09/2026) : les fiches de jeux de données ont été ouvertes et lues ; les services WMS/WFS et les fichiers n'ont pas été interrogés ni téléchargés. « Titre repéré, non ouvert » = trouvé par recherche seulement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
         <is>
           <t>Le document de capacités WFS et WMTS de la Géoplateforme a été interrogé dans un navigateur le 21/09/2026 : les noms de couches patrinat_* cités ici y figurent. Aucune requête de données (GetFeature) n'a encore été testée.</t>
         </is>
@@ -1272,7 +1301,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C49"/>
+  <dimension ref="A1:C50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -2110,6 +2139,23 @@
       <c r="C49" s="7" t="inlineStr">
         <is>
           <t>Fiche lue le 25/09/2026 (licence, ressources) ; WFS du Shom interrogé le même jour</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="7" t="inlineStr">
+        <is>
+          <t>ZMEL (données réelles converties, non branchées)</t>
+        </is>
+      </c>
+      <c r="B50" s="8" t="inlineStr">
+        <is>
+          <t>https://legicem.metier.e2.rie.gouv.fr/gavres-a4915.html</t>
+        </is>
+      </c>
+      <c r="C50" s="7" t="inlineStr">
+        <is>
+          <t>Testée le 25/09/2026 : injoignable depuis l'extérieur (échec de connexion, domaine RIE), non ouverte avec succès — champ url_v2 du jeu de données, inutilisable pour un contact public</t>
         </is>
       </c>
     </row>

--- a/data/donnees_carte_amidomar.xlsx
+++ b/data/donnees_carte_amidomar.xlsx
@@ -901,42 +901,37 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>ZMEL</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>data/zmel.geojson</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>GeoJSON, 1 polygone fictif</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr"/>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>données simulées</t>
-        </is>
-      </c>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>Méditerranée (Corse, Languedoc-Roussillon, PACA) : jeu DIRM Méditerranée, shapefile, WMS/WFS, Licence Ouverte 2.0, publié en 2021. Attention : c'est une interprétation des textes, pas la réglementation officielle. Il peut aussi combler le jeu du Var signalé en panne. https://catalogue.sigena.fr/geonetwork/srv/api/records/fr-120066022-jdd-86ec0654-0c2c-4e76-a9a0-abb36d978d34
-Charente-Maritime (DDTM 17) : shapefile, WMS/WFS, mis à jour en 2024 : https://www.data.gouv.fr/datasets/zones-de-mouillages-et-dequipements-legers-zmel-en-charente-maritime
-Finistère (DDTM 29, jeu archivé, donnée d'avril 2025) : https://www.data.gouv.fr/datasets/mouillages-groupes-du-finistere-1/
-Morbihan (titre repéré, non ouvert) : https://www.data.gouv.fr/datasets/zones-de-mouillage-et-dequipements-legers-zmel-departement-du-morbihan-1
-Vue nationale : 260 ZMEL dans 209 communes sur GéoLittoral, sans téléchargement annoncé ; demande possible à geolittoral@cerema.fr : https://www.geolittoral.developpement-durable.gouv.fr/zones-de-mouillage-et-d-equipements-legers-a1757.html?lang=fr
-25/09/2026 : Nicolas a fourni un shapefile Cerema/CACEM (647 ZMEL, France entière) — converti dans data/zmel-reel.geojson (voir ligne ci-dessous), mais pas encore branché ici.</t>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>data/zmel.geojson — shapefile Cerema/CACEM fourni par Nicolas (ZMEL_18_09_2026), converti et branché</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>GeoJSON, 647 polygones/multipolygones, France entière + Antilles</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>données fonctionnelles</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="n"/>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Branché le 25/09/2026 (v2.10), remplace l'ancien fichier fictif. Reste à améliorer : nb_postes_ est un total agrégé en texte (pas de détail par catégorie de navire affiché) ; aucun contact e-mail dans la source (voir ligne ci-dessous pour le détail de la conversion et la tentative infructueuse de récupération de contacts via Légicem). Champs redev_an_z/redev_an_p (redevance) présents dans la donnée mais volontairement pas affichés au public.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>ZMEL (données réelles converties, non branchées)</t>
+          <t>ZMEL — source de la conversion (shapefile d'origine)</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
@@ -952,7 +947,7 @@
       <c r="D16" s="4" t="n"/>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>Converti et vérifié géométriquement (bbox plausible, 0 entité perdue) le 25/09/2026, mais PAS ENCORE branché sur la carte (data/zmel.geojson, fictif, reste la source active). Schéma d'attributs différent de celui attendu par modaleZmel() : nb_postes_ est un total agrégé en texte (pas de nombre par navire simple), pas de champ e-mail/contact. Lien url_v2 (fiches Légicem) injoignable depuis l'extérieur : domaine legicem.metier.e2.rie.gouv.fr sur le RIE (réseau interministériel de l'État), échec de connexion confirmé le 25/09/2026 — inutilisable pour récupérer un contact, y compris pour le public. Champ redev_an_z/redev_an_p (redevance) présent mais volontairement pas prévu à l'affichage public (sensible).</t>
+          <t>Converti et vérifié géométriquement (bbox plausible, 0 entité perdue) le 25/09/2026, puis branché sur la carte le même jour (v2.10) : data/zmel.geojson est désormais une copie conforme de ce fichier. Schéma d'attributs différent de celui attendu par modaleZmel() : nb_postes_ est un total agrégé en texte (pas de nombre par navire simple), pas de champ e-mail/contact. Lien url_v2 (fiches Légicem) injoignable depuis l'extérieur : domaine legicem.metier.e2.rie.gouv.fr sur le RIE (réseau interministériel de l'État), échec de connexion confirmé le 25/09/2026 — inutilisable pour récupérer un contact, y compris pour le public. Champ redev_an_z/redev_an_p (redevance) présent mais volontairement pas prévu à l'affichage public (sensible).</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">

--- a/data/donnees_carte_amidomar.xlsx
+++ b/data/donnees_carte_amidomar.xlsx
@@ -47,7 +47,7 @@
       <u val="single"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -67,6 +67,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2F0D9"/>
+        <bgColor rgb="00E2F0D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+        <bgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -96,7 +108,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -114,6 +126,12 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -479,7 +497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -565,94 +583,126 @@
       <c r="D3" s="3" t="inlineStr"/>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>Ce qui ne va pas : pour savoir si un point est en mer ou à terre, l'application regarde la couleur du fond de carte à cet endroit. C'est fragile (plage, marais, changement de style).
-Ce qu'il faut : un tracé précis de la limite terre/mer.</t>
+          <t>Ce qui ne va pas : plus la seule source du verdict depuis le 12/10/2026 (v2.14). La lecture de la couleur du fond de carte reste la réponse instantanée et le repli quand le réseau manque, mais elle n'est plus décisive : un verdict « à terre » est arbitré par le trait terre-mer du Shom (ligne ci-dessous).
+Ce qu'il faut : décider, après la phase de test auprès des DDTM pilotes, si la carte fantôme peut être supprimée — elle coûte une seconde carte MapLibre invisible et son jeu de tuiles.</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>Limite terre-mer (Shom) : ligne des plus hautes mers, France métropolitaine, précision 1 à 5 m, en shapefile, GeoJSON, WFS, WMS et tuiles vectorielles, Licence Ouverte 2.0, mise à jour le 21/09/2026. Permet un vrai test « le point est-il du côté mer ? ». https://www.data.gouv.fr/datasets/limite-terre-mer-1
-Le trait de côte Histolitt (https://www.data.gouv.fr/datasets/trait-de-cote-histolitt) est à réserver à l'outre-mer : la page recommande Limite terre-mer pour la métropole.</t>
+          <t>Résolu le 12/10/2026 par la Limite terre-mer du Shom, branchée au clic : voir la ligne « Limite terre-mer (verdict terre/mer au clic) » ci-dessous.
+Le trait de côte Histolitt (https://www.data.gouv.fr/datasets/trait-de-cote-histolitt) reste à réserver à l'outre-mer : la page recommande Limite terre-mer pour la métropole, et c'est bien le produit métropolitain qui est utilisé.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>Limite terre-mer (verdict terre/mer au clic)</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>SHOM-IGN, LIMTM 2021, services INSPIRE (data.shom.fr)</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>WFS 2.0.0, GeoJSON, filtre INTERSECTS au point ; couche non affichée</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>données fonctionnelles</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="n"/>
+      <c r="F4" s="9" t="inlineStr">
+        <is>
+          <t>Branché le 12/10/2026 (v2.14). Couche LIMTM_2154_WFS:limite_terre_mer_france_metropolitaine_polygones, qui porte les SURFACES TERRESTRES : zéro objet renvoyé = point côté mer, estran compris. Le produit matérialise la laisse des plus hautes mers astronomiques (coefficient 120, météo normale), soit la limite du DPM naturel au sens de l'article L2111-4 du CGPPP, à 1 à 5 m de résolution.
+Testé en réel le 12/10/2026 depuis le navigateur, sur quatre points : anse de Pen Hat et rade d'Hyères renvoient « mer », le bourg de Camaret renvoie « terre » avec numdep = 29, et l'estran de la baie du Mont-Saint-Michel (+13 m au-dessus du niveau de référence) renvoie bien « mer ». Réponses de 56 à 207 ms, 150 à 300 octets.
+Attention : la couche est en Lambert 93, le préfixe SRID=4326; du filtre est obligatoire — sans lui le service renvoie zéro objet, ce qui se lirait à tort comme « en mer ».
+Limites connues : France métropolitaine seulement (hors métropole, repli sur la détection locale) ; millésime 2021 ; produit « non certifié pour la navigation ». Licence Ouverte 2.0, citation obligatoire « Shom-IGN, 2021. https://dx.doi.org/10.17183/LIMTM », portée par l'attribution de la carte.
+Reste à faire : le rattachement d'un point EN MER à une DDTM n'est pas couvert (numdep n'existe que pour les points à terre, et le Shom ne diffuse que des lignes de limites administratives, pas des polygones) — question reposée au Shom.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>Fond « aérien »</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>IGN via Carte Facile</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>Tuiles raster</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr"/>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr"/>
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>Ce qui ne va pas : jamais testé, on ne sait pas s'il marche.
 Ce qu'il faut : le tester sur les 7 sites.</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>Pas de source à chercher : c'est un test à faire sur l'existant.</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>Recherche de lieu</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>Géocodage Géoplateforme IGN</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>JSON</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>données fonctionnelles</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr"/>
-      <c r="F5" s="2" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr"/>
+      <c r="F6" s="2" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>Natura 2000 habitats (SIC/ZSC), affichage</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>IGN / INPN, Patrinat_SIC</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>WMTS, tuiles PNG raster</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr"/>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr"/>
+      <c r="E7" s="3" t="inlineStr">
         <is>
           <t>Ce qui ne va pas : la zone s'affiche comme une image, donc l'application ne peut pas calculer si le mouillage est dedans ou à quelle distance. À Brest la carte reste vide, sans explication.
 Ce qu'il faut : les contours en données, et vérifier Brest.</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="F7" s="3" t="inlineStr">
         <is>
           <t>La Géoplateforme expose la couche patrinat_sic en WFS (contours en données) : https://data.geopf.fr/wfs?REQUEST=GetCapabilities&amp;SERVICE=WFS&amp;VERSION=2.0.0 (nom confirmé). Test réel du 21/09/2026 dans un navigateur : requête WFS GetFeature sur la Géoplateforme, filtrée sur un point (CQL_FILTER=INTERSECTS(geom,SRID=4326;POINT(lon lat)), champ du nom : nom_site). Résultat sur 6 points en mer : Rade d'Hyères (Port-Cros), Plateau de Pertusato / Bonifacio et îles Lavezzi, Golfe du Morbihan côte ouest de Rhuys, Rade de Brest estuaire de l'Aulne, Golfe d'Ajaccio ; aucun site au large de Quiberon. Réponses de quelques ko, de 0,1 à 2,5 s (une première requête à 11 s). Les contours existent donc à Brest : la carte vide y vient de l'affichage en image, pas de la donnée..
 À éviter : les jeux « Natura 2000 ZSC/ZPS » de data.gouv.fr sont publiés par la Région Île-de-France, donc sans zones marines : https://www.data.gouv.fr/datasets/natura-2000-zones-speciales-de-conservation-zsc
@@ -660,118 +710,118 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>Natura 2000 oiseaux (ZPS), affichage</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>IGN / INPN, Patrinat_ZPS</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>WMTS, tuiles PNG raster</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr"/>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr"/>
+      <c r="E8" s="3" t="inlineStr">
         <is>
           <t>Ce qui ne va pas : mêmes problèmes que pour les habitats : zone visible mais non calculable, carte vide à Brest.
 Ce qu'il faut : les contours en données, et vérifier Brest.</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="F8" s="3" t="inlineStr">
         <is>
           <t>Couche patrinat_zps exposée en WFS par la Géoplateforme (même service). Test réel du 21/09/2026 dans un navigateur : requête WFS GetFeature sur la Géoplateforme, filtrée sur un point (CQL_FILTER=INTERSECTS(geom,SRID=4326;POINT(lon lat)), champ du nom : nom_site). Résultat : Iles d'Hyères, Iles Lavezzi Bouches de Bonifacio, Golfe du Morbihan, Rade de Brest Baie de Daoulas, Iles Sanguinaires golfe d'Ajaccio, Camargue ; rien au large de Quiberon. : https://data.geopf.fr/wfs?REQUEST=GetCapabilities&amp;SERVICE=WFS&amp;VERSION=2.0.0</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>Parcs naturels marins, affichage</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>IGN / INPN, Patrinat_PNM</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>WMTS, tuiles PNG raster</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr"/>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr"/>
+      <c r="E9" s="3" t="inlineStr">
         <is>
           <t>Ce qui ne va pas : le parc est visible, mais un clic ne dit pas dans quel parc on est.
 Ce qu'il faut : identifier le parc au clic, et connaître les règles de chaque parc (charte, zones renforcées).</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="F9" s="3" t="inlineStr">
         <is>
           <t>Les parcs naturels marins font partie des aires marines protégées de l'OFB, avec leur catégorie : voir la ligne « Aires marines protégées ». La Géoplateforme liste aussi une couche patrinat_pnm en WFS (à confirmer qu'il s'agit bien des parcs naturels marins). Les règles de chaque parc sont à demander aux parcs : aucun jeu de données ouvert trouvé.</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>ZNIEFF marines type 1, affichage</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>IGN / INPN, Patrinat_ZNIEFF1_MER</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>WMTS, tuiles PNG raster</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr"/>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr"/>
+      <c r="E10" s="3" t="inlineStr">
         <is>
           <t>Ce qui ne va pas : zone visible mais un clic ne dit pas de quelle ZNIEFF il s'agit (les données de clic ne renvoient que des zones terrestres). Une partie de la carte ne se charge pas à Ajaccio. Le type 2 existe mais n'est pas affiché.
 Ce qu'il faut : les contours en données, le clic pour la mer, le type 2.</t>
         </is>
       </c>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="F10" s="3" t="inlineStr">
         <is>
           <t>Jeu INPN ZNIEFF sur data.gouv.fr : France entière, terrestre et marin, 14 fichiers shapefile, mise à jour du 17/09/2026 : https://www.data.gouv.fr/datasets/inpn-donnees-du-programme-znieff (téléchargement à charger dans la carte, ou à héberger).
 La Géoplateforme liste patrinat_znieff1_mer et patrinat_znieff2_mer en WFS, et Patrinat_ZNIEFF2_MER en WMTS (noms confirmés). Le filtre par point fonctionne sur znieff1_mer (test sur un sommet de l'Île Riou, Marseille : « ILE RIOU, ILOTS CONGLUÉ ET IMPÉRIAUX ») et sur znieff2_mer ; aucun des 6 points en mer testés (Port-Cros, Lavezzi, Morbihan, Brest, Ajaccio, Beauduc) n'était dans une ZNIEFF marine, ce qui reste à vérifier sur des zones connues : https://data.geopf.fr/wfs?REQUEST=GetCapabilities&amp;SERVICE=WFS&amp;VERSION=2.0.0</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>Aires marines protégées</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>OFB, wxs.ofb.fr</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>WMS 1.1.1, PNG raster</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr"/>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr"/>
+      <c r="E11" s="3" t="inlineStr">
         <is>
           <t>Ce qui ne va pas : les aires s'affichent partout, mais un clic ne dit pas de quelle aire il s'agit, ni son niveau de protection.
 Ce qu'il faut : les contours en données, avec la catégorie de protection.</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="F11" s="3" t="inlineStr">
         <is>
           <t>La fiche OFB décrit des polygones avec plus de 26 attributs (dont la catégorie nationale), diffusés en WFS et WMS sur wxs.ofb.fr/geoserver : https://data.ofb.fr/catalogue/srv/api/records/7bb33d95-7950-499a-9bd8-6f31d58b0b35
 Portail AMP et ses webservices : https://www.amp.milieumarinfrance.fr/accueil-fr/webservices
@@ -779,30 +829,30 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>Herbiers de posidonie</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>Ifremer Sextant, BIOMED Palavas et Albères</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>WMS 1.1.1, PNG raster</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr"/>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="D12" s="3" t="inlineStr"/>
+      <c r="E12" s="3" t="inlineStr">
         <is>
           <t>Ce qui ne va pas : les herbiers n'apparaissent presque qu'en Occitanie (Palavas, Albères), nulle part ailleurs (Hyères, Corse, Quiberon, Brest, Arcachon). La légende annonce la zostère, absente de cette source.
 Ce qu'il faut : une source couvrant tout le littoral, avec les contours en données.</t>
         </is>
       </c>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="F12" s="3" t="inlineStr">
         <is>
           <t>Inventaire national des herbiers de posidonie (OFB, polygones) : shapefile, WMS et WFS, Licence Ouverte 2.0, mis à jour en 2025-2026. À vérifier : la page indique un périmètre limité aux sites Natura 2000 marins, donc la couverture de Hyères et de la Corse est à contrôler. https://www.data.gouv.fr/datasets/inventaire-des-donnees-disponibles-spatialisant-les-herbiers-de-posidonie-en-france-metropolitaine-polygone
 Version posidonie et zostère : https://www.data.gouv.fr/datasets/inventaire-des-donnees-disponibles-spatialisant-les-herbiers-de-posidonie-et-de-zostere-en-france-metropolitaine
@@ -812,173 +862,173 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>Informations portuaires</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>SHOM, services INSPIRE</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>WMS 1.1.1, PNG raster (symboles)</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr"/>
-      <c r="E12" s="3" t="inlineStr">
+      <c r="D13" s="3" t="inlineStr"/>
+      <c r="E13" s="3" t="inlineStr">
         <is>
           <t>Ce qui ne va pas : les symboles de ports s'affichent, mais sans information (nom, gestionnaire, limites).
 Ce qu'il faut : une liste des ports avec ces informations.</t>
         </is>
       </c>
-      <c r="F12" s="3" t="inlineStr">
+      <c r="F13" s="3" t="inlineStr">
         <is>
           <t>Le même jeu Shom existe en données (shapefile, WFS, WMS) avec 13 classes d'objets dont zones portuaires et fonctions du port (plaisance, pêche) : https://www.data.gouv.fr/datasets/informations-portuaires-1 (la présence du nom et du gestionnaire n'est pas confirmée).
 Pour les gestionnaires et capacités : Observatoire des ports de plaisance, voir la ligne « Ports de plaisance ».</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>Natura 2000 au clic</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>API Carto IGN, /nature/natura-habitat et /nature/natura-oiseaux</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>JSON</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>données fonctionnelles</t>
         </is>
       </c>
-      <c r="E13" s="2" t="n"/>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="E14" s="2" t="n"/>
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>Corrigé dans index.html le 21/09/2026 (endpoints natura-habitat et natura-oiseaux, champ sitename, délai porté à 8 s) et testé en réel sur 5 points (Port-Cros, Lavezzi, golfe du Morbihan, Beauduc, large de Quiberon). Non testé sur Brest. Le nom de site est bien identifié, mais les zones Natura 2000 restent affichées en image (voir lignes d'affichage).
 Repli branché le 21/09/2026 (v1.9) : si l'API Carto échoue, la carte interroge le WFS de la Géoplateforme (patrinat_sic, patrinat_zps). Test réel : l'API Carto a dépassé 8 s sur 2 requêtes Natura 2000 à Port-Cros, le repli a rendu « Rade d'Hyères » et « Iles d'Hyères ».</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>ZNIEFF au clic</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>API Carto IGN, znieff1 et znieff2</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>JSON</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr"/>
-      <c r="E14" s="3" t="inlineStr">
+      <c r="D15" s="3" t="inlineStr"/>
+      <c r="E15" s="3" t="inlineStr">
         <is>
           <t>Ce qui ne va pas : l'API Carto ne renvoie rien en mer pour les ZNIEFF. Un repli sur le WFS de la Géoplateforme (couches marines znieff1_mer et znieff2_mer) est branché depuis le 21/09/2026 ; il n'est confirmé que sur un point marin (Île Riou), pas sur la carte publiée.
 Ce qu'il faut : tester sur d'autres ZNIEFF marines connues une fois la version en ligne.</t>
         </is>
       </c>
-      <c r="F14" s="3" t="inlineStr">
+      <c r="F15" s="3" t="inlineStr">
         <is>
           <t>Repli WFS (v1.9) : patrinat_znieff1_mer et patrinat_znieff2_mer, filtre INTERSECTS sur le point cliqué. Test réel du 21/09/2026 : Île Riou → « ILE RIOU, ILOTS CONGLUÉ ET IMPÉRIAUX » (l'API Carto avait dépassé 8 s). Alternative : charger le jeu INPN complet : https://www.data.gouv.fr/datasets/inpn-donnees-du-programme-znieff</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>ZMEL</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>data/zmel.geojson — shapefile Cerema/CACEM fourni par Nicolas (ZMEL_18_09_2026), converti et branché</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>GeoJSON, 647 polygones/multipolygones, France entière + Antilles</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>données fonctionnelles</t>
         </is>
       </c>
-      <c r="E15" s="2" t="n"/>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="E16" s="2" t="n"/>
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>Branché le 25/09/2026 (v2.10), remplace l'ancien fichier fictif. Reste à améliorer : nb_postes_ est un total agrégé en texte (pas de détail par catégorie de navire affiché) ; aucun contact e-mail dans la source (voir ligne ci-dessous pour le détail de la conversion et la tentative infructueuse de récupération de contacts via Légicem). Champs redev_an_z/redev_an_p (redevance) présents dans la donnée mais volontairement pas affichés au public.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>ZMEL — source de la conversion (shapefile d'origine)</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>data/zmel-reel.geojson — shapefile Cerema/CACEM fourni par Nicolas (ZMEL_18_09_2026), converti</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>GeoJSON, 647 polygones/multipolygones, France entière + Antilles, reprojeté Lambert-93 → WGS84</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="n"/>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>Converti et vérifié géométriquement (bbox plausible, 0 entité perdue) le 25/09/2026, puis branché sur la carte le même jour (v2.10) : data/zmel.geojson est désormais une copie conforme de ce fichier. Schéma d'attributs différent de celui attendu par modaleZmel() : nb_postes_ est un total agrégé en texte (pas de nombre par navire simple), pas de champ e-mail/contact. Lien url_v2 (fiches Légicem) injoignable depuis l'extérieur : domaine legicem.metier.e2.rie.gouv.fr sur le RIE (réseau interministériel de l'État), échec de connexion confirmé le 25/09/2026 — inutilisable pour récupérer un contact, y compris pour le public. Champ redev_an_z/redev_an_p (redevance) présent mais volontairement pas prévu à l'affichage public (sensible).</t>
-        </is>
-      </c>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>Shapefile fourni directement par Nicolas le 25/09/2026 (source Cerema/CACEM, pas encore identifiée avec certitude comme le jeu GéoLittoral national mentionné ligne ZMEL ci-dessus — à confirmer). Reste à faire pour brancher : ajouter une entrée COUCHES pointant sur ce fichier, adapter ou étendre modaleZmel() si besoin, décider du remplacement (ou non) de data/zmel.geojson.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
+          <t>ZMEL — source de la conversion (shapefile d'origine)</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>data/zmel-reel.geojson — shapefile Cerema/CACEM fourni par Nicolas (ZMEL_18_09_2026), converti</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>GeoJSON, 647 polygones/multipolygones, France entière + Antilles, reprojeté Lambert-93 → WGS84</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="n"/>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>Converti et vérifié géométriquement (bbox plausible, 0 entité perdue) le 25/09/2026, puis branché sur la carte le même jour (v2.10) : data/zmel.geojson est désormais une copie conforme de ce fichier. Schéma d'attributs différent de celui attendu par modaleZmel() : nb_postes_ est un total agrégé en texte (pas de nombre par navire simple), pas de champ e-mail/contact. Lien url_v2 (fiches Légicem) injoignable depuis l'extérieur : domaine legicem.metier.e2.rie.gouv.fr sur le RIE (réseau interministériel de l'État), échec de connexion confirmé le 25/09/2026 — inutilisable pour récupérer un contact, y compris pour le public. Champ redev_an_z/redev_an_p (redevance) présent mais volontairement pas prévu à l'affichage public (sensible).</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>Shapefile fourni directement par Nicolas le 25/09/2026 (source Cerema/CACEM, pas encore identifiée avec certitude comme le jeu GéoLittoral national mentionné ligne ZMEL ci-dessus — à confirmer). Reste à faire pour brancher : ajouter une entrée COUCHES pointant sur ce fichier, adapter ou étendre modaleZmel() si besoin, décider du remplacement (ou non) de data/zmel.geojson.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
           <t>Cultures marines</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>data/cultures-marines.geojson</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C18" s="4" t="inlineStr">
         <is>
           <t>GeoJSON, 1 polygone fictif</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr"/>
-      <c r="E17" s="4" t="inlineStr">
+      <c r="D18" s="4" t="inlineStr"/>
+      <c r="E18" s="4" t="inlineStr">
         <is>
           <t>données simulées</t>
         </is>
       </c>
-      <c r="F17" s="4" t="inlineStr">
+      <c r="F18" s="4" t="inlineStr">
         <is>
           <t>Aucun cadastre conchylicole national trouvé : il se récupère département par département.
 Manche (DDTM 50, shapefile, WMS/WFS, 2025) : https://www.data.gouv.fr/datasets/cadastre-conchylicole-1
@@ -989,29 +1039,29 @@
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>Ports de plaisance (places, contact)</t>
         </is>
       </c>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>data/ports-plaisance.geojson</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t>GeoJSON, 6 points</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr"/>
-      <c r="E18" s="4" t="inlineStr">
+      <c r="D19" s="4" t="inlineStr"/>
+      <c r="E19" s="4" t="inlineStr">
         <is>
           <t>données simulées</t>
         </is>
       </c>
-      <c r="F18" s="4" t="inlineStr">
+      <c r="F19" s="4" t="inlineStr">
         <is>
           <t>Observatoire des ports de plaisance (Ministère, GéoLittoral) : 488 ports en métropole ; la page annonce des capacités d'accueil et des certifications téléchargeables sur son portail de données (format et licence non vérifiés) : https://www.geolittoral.developpement-durable.gouv.fr/observatoire-des-ports-de-plaisance-a1733.html?lang=fr
 Caractéristiques des ports en France 2021 (PIGMA, titre repéré, non ouvert) : https://www.pigma.org/geonetwork/5a8srv/api/records/00c61236-da83-4215-ab58-b0ee88925cf4
@@ -1019,29 +1069,29 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>AOT existantes</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>data/aot-existantes.geojson</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C20" s="4" t="inlineStr">
         <is>
           <t>GeoJSON, 249 points</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr"/>
-      <c r="E19" s="4" t="inlineStr">
+      <c r="D20" s="4" t="inlineStr"/>
+      <c r="E20" s="4" t="inlineStr">
         <is>
           <t>données simulées</t>
         </is>
       </c>
-      <c r="F19" s="4" t="inlineStr">
+      <c r="F20" s="4" t="inlineStr">
         <is>
           <t>Des positions réelles sont déjà publiées :
 Finistère (DDTM 29) : mouillages individuels sous AOT représentés par un cercle, shapefile, WMS/WFS, extraction ADOC du 28/05/2026, mis à jour le 29/05/2026. Les champs (longueur, statut) ne sont pas documentés sur la page : https://www.data.gouv.fr/datasets/mouillages-individuels-du-finistere-1
@@ -1050,30 +1100,30 @@
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>Profondeur au point (colonne d'eau à marée haute)</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>EMODnet Bathymetry, API depth_sample (grille européenne intégrant les levés du Shom)</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="C21" s="3" t="inlineStr">
         <is>
           <t>JSON (REST), maille d'environ 115 m</t>
         </is>
       </c>
-      <c r="D20" s="3" t="inlineStr"/>
-      <c r="E20" s="3" t="inlineStr">
+      <c r="D21" s="3" t="inlineStr"/>
+      <c r="E21" s="3" t="inlineStr">
         <is>
           <t>Ce qui ne va pas : branché en v2.6 (25/09/2026) et testé sur l'API réelle, mais le clic complet sur la carte publiée avec l'API réelle reste à vérifier ; la maille d'environ 115 m donne un fond moyen, peu fidèle près des roches et des chenaux.
 Ce qu'il faut : un test en conditions réelles sur la carte publiée, puis, si besoin, une bathymétrie plus fine sur les zones pilotes (MNT côtiers du Shom à 5-20 m).</t>
         </is>
       </c>
-      <c r="F20" s="3" t="inlineStr">
+      <c r="F21" s="3" t="inlineStr">
         <is>
           <t>API testée le 25/09/2026 depuis le site publié : CORS accepté, 60 à 370 ms ; Quiberon −12,35 m, Brest −23,6 m, Saint-Malo −1,86 m. https://rest.emodnet-bathymetry.eu/depth_sample?geom=POINT(-2.970485 47.510572)
 Écartés : WMS « MNT » du Shom non interrogeable au point (LayerNotQueryable), export image/x-bil incohérent (tests du 25/09/2026).
@@ -1082,60 +1132,60 @@
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="3" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
         <is>
           <t>Hauteur de marée haute (colonne d'eau à marée haute)</t>
         </is>
       </c>
-      <c r="B21" s="3" t="inlineStr">
+      <c r="B22" s="3" t="inlineStr">
         <is>
           <t>data/ram-ports.json, extrait du Shom, Références Altimétriques Maritimes (WFS RAM_BDD_WLD_WGS84G_WFS:ram_3857)</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr">
+      <c r="C22" s="3" t="inlineStr">
         <is>
           <t>JSON, 214 ports (métropole)</t>
         </is>
       </c>
-      <c r="D21" s="3" t="n"/>
-      <c r="E21" s="3" t="inlineStr">
+      <c r="D22" s="3" t="n"/>
+      <c r="E22" s="3" t="inlineStr">
         <is>
           <t>Ce qui ne va pas : valeur fixe par port (vives-eaux moyennes, coefficient 95), pas la marée du jour ; port choisi à vol d'oiseau, parfois de l'autre côté d'une pointe ; 15 ports sans valeurs exploitables écartés ; extraction du 25/09/2026 à rafraîchir si le Shom publie une nouvelle édition.
 Ce qu'il faut : garder la table à jour ; pour la marée du jour, un abonnement aux API de prédiction du Shom (payant) avec un petit serveur intermédiaire.</t>
         </is>
       </c>
-      <c r="F21" s="3" t="inlineStr">
+      <c r="F22" s="3" t="inlineStr">
         <is>
           <t>Source ouverte (Licence Ouverte, citer « Shom, 2025 ») : https://www.data.gouv.fr/datasets/references-altimetriques-maritimes — WFS interrogé le 25/09/2026 (446 sites, 229 en métropole, sommes de contrôle notées dans TESTS_FONCTIONNELS.md §5/9quinquies).
 API marée du Shom (payantes, clé) : https://diffusion.shom.fr/api-shom.html</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>Vent, courant, nature du fond</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>Vent et courant (calcul du rayon d’évitage)</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
         <is>
           <t>Aucune</t>
         </is>
       </c>
-      <c r="C22" s="3" t="inlineStr">
+      <c r="C23" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D22" s="3" t="inlineStr"/>
-      <c r="E22" s="3" t="inlineStr">
-        <is>
-          <t>Ce qui ne va pas : le calcul du rayon d'évitage ignore le vent, le courant et le type de fond, qui changent la zone réellement balayée par le bateau.
-Ce qu'il faut : ces trois données.</t>
-        </is>
-      </c>
-      <c r="F22" s="3" t="inlineStr">
+      <c r="D23" s="3" t="inlineStr"/>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>Ce qui ne va pas : le calcul du rayon d'évitage ne tient compte ni du vent ni du courant. La nature du fond, elle, est branchée depuis le 12/10/2026 (ligne ci-dessous) mais n'entre pas dans le calcul : elle sert au conseil d'ancrage.
+Ce qu'il faut : décider si le rayon d'évitage doit intégrer ces paramètres, sachant que le produit resterait indicatif.</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
         <is>
           <t>Nature du fond : Natures de fond au 1/50 000 (Shom), 47 cartes, shapefile et GML, WMS/WMTS/WFS, gratuit, version 2025 : https://diffusion.shom.fr/donnees/sedimentologie/natures-de-fond.html
 Courants : la page Shom des courants de marée 2D était inaccessible au test, et l'API Shom ne liste ni courants ni vent (marées payantes) : https://diffusion.shom.fr/services-numeriques/api-shom.html
@@ -1144,142 +1194,176 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="3" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="10" t="inlineStr">
+        <is>
+          <t>Nature du fond au clic (conseil d’ancrage)</t>
+        </is>
+      </c>
+      <c r="B24" s="10" t="inlineStr">
+        <is>
+          <t>SHOM, Natures de fond au 1/50 000, 2025, services INSPIRE</t>
+        </is>
+      </c>
+      <c r="C24" s="10" t="inlineStr">
+        <is>
+          <t>WFS 2.0.0, GeoJSON, filtre INTERSECTS au point ; couche non affichée</t>
+        </is>
+      </c>
+      <c r="D24" s="10" t="n"/>
+      <c r="E24" s="10" t="inlineStr">
+        <is>
+          <t>Ce qui ne va pas : la couverture n'est pas nationale. Taux de réponse mesuré le 12/10/2026 sur 30 points en mer tirés au hasard par territoire : Morbihan 100 %, Var 97 %, Finistère 87 %, mais Ille-et-Vilaine 27 % et Côtes-d'Armor 3 %. Le produit synthétise 45 cartes sédimentaires publiées de 1990 à 2023, et les feuilles non publiées laissent des trous.
+Autre limite : c'est une carte SÉDIMENTAIRE, elle ne représente pas les herbiers. Un fond de sable n'exclut pas un herbier.
+Ce qu'il faut : demander au Shom le calendrier de publication des feuilles manquantes, en priorité sur les Côtes-d'Armor (territoire pilote).</t>
+        </is>
+      </c>
+      <c r="F24" s="10" t="inlineStr">
+        <is>
+          <t>Branché le 12/10/2026 (v2.15). Couche NDF_BDD_WLD_WGS84G_WFS:natures_fond_50000, attribut typelem, interrogée en parallèle des zonages. Affichée uniquement quand le mouillage n'est pas interdit.
+Table des 24 libellés établie le 12/10/2026 sans déduction : extraction de la légende officielle (GetLegendGraphic, 33 entrées), puis comparaison, pour chaque code, de la couleur réellement rendue par le WMS au point avec la pastille de légende — 23 correspondances exactes sur 24. Seul NFSFC (un unique polygone en France) est déduit.
+Répartition nationale (28 534 polygones) : Roche 49,9 %, Sables 12,7 %, Graviers 8,9 %, Sables et graviers 7,6 %, Sables fins 5,1 %, le reste sous 4 %.
+Conseil associé volontairement environnemental (page « Bien mouiller »), jamais une appréciation de tenue d'ancre : le produit porte la mention « ne pas utiliser pour la navigation ».
+Licence Ouverte 2.0, citation obligatoire « Shom, 2025. Natures de fond au 1/50 000, https://dx.doi.org/10.17183/HOM_GEOL_NATURES_FOND_50 », portée par l'attribution de la carte.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
         <is>
           <t>Réserves naturelles nationales</t>
         </is>
       </c>
-      <c r="B23" s="3" t="inlineStr">
+      <c r="B25" s="3" t="inlineStr">
         <is>
           <t>Patrinat_RNN (Géoplateforme)</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr">
+      <c r="C25" s="3" t="inlineStr">
         <is>
           <t>Non testé</t>
         </is>
       </c>
-      <c r="D23" s="3" t="inlineStr"/>
-      <c r="E23" s="3" t="inlineStr">
+      <c r="D25" s="3" t="inlineStr"/>
+      <c r="E25" s="3" t="inlineStr">
         <is>
           <t>Ce qui ne va pas : la couche existe mais n'est pas sur la carte, alors que la note la donne « en service ».
 Ce qu'il faut : l'ajouter et la tester.</t>
         </is>
       </c>
-      <c r="F23" s="3" t="inlineStr">
+      <c r="F25" s="3" t="inlineStr">
         <is>
           <t>Couche patrinat_rnn confirmée dans le document de capacités WFS de la Géoplateforme (21/09/2026) : https://data.geopf.fr/wfs?REQUEST=GetCapabilities&amp;SERVICE=WFS&amp;VERSION=2.0.0</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>Arrêtés de protection de biotope (APB)</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>IGN / INPN, Patrinat_APB</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>WMTS, tuiles PNG raster</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>données fonctionnelles</t>
         </is>
       </c>
-      <c r="E24" s="2" t="n"/>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="E26" s="2" t="n"/>
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>Affichage : couche patrinat_apb confirmée en WFS et en WMTS le 21/09/2026 ; polygones vus au Morbihan (zoom 11), couleur de légende orange alignée sur les tuiles.
 Au clic (v2.0, 22/09/2026) : couche patrinat_apb:apb, champ nom_site, filtre INTERSECTS. Testé en direct sur l'APB « Ile Dumet et ses abords » (centre du polygone, pas un sommet) : nom renvoyé en ~480 ms. Traité comme une interdiction bloquante, prioritaire sur Natura 2000/ZNIEFF (popup rouge, pas de coordonnées), vérifiée avant tout affichage (délai 4 s, défaut non bloquant). Reste à tester : un clic réel dans un APB sur la carte publiée.</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="3" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
         <is>
           <t>Autres zonages (Ramsar, RNR, Conservatoire du littoral)</t>
         </is>
       </c>
-      <c r="B25" s="3" t="inlineStr">
+      <c r="B27" s="3" t="inlineStr">
         <is>
           <t>Patrinat_RAMSAR, Patrinat_RNR, CONSERVATOIRE_LITTORAL.PERIMETRES</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr">
+      <c r="C27" s="3" t="inlineStr">
         <is>
           <t>Non testé</t>
         </is>
       </c>
-      <c r="D25" s="3" t="inlineStr"/>
-      <c r="E25" s="3" t="inlineStr">
+      <c r="D27" s="3" t="inlineStr"/>
+      <c r="E27" s="3" t="inlineStr">
         <is>
           <t>Ce qui ne va pas : couches existantes mais absentes de la carte.
 Ce qu'il faut : décider si le besoin métier justifie de les ajouter, puis vérifier le rendu.</t>
         </is>
       </c>
-      <c r="F25" s="3" t="inlineStr">
+      <c r="F27" s="3" t="inlineStr">
         <is>
           <t>WFS Géoplateforme : patrinat_ramsar et CONSERVATOIRE_LITTORAL.PERIMETRES sont listées ; patrinat_rnr y figure aussi (noms confirmés le 21/09/2026 ; requêtes de données non testées) : https://data.geopf.fr/wfs?REQUEST=GetCapabilities&amp;SERVICE=WFS&amp;VERSION=2.0.0
 Espaces protégés du Conservatoire du littoral (titre repéré, non ouvert) : https://www.data.gouv.fr/datasets/site-des-espaces-proteges-du-conservatoire-du-littoral</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="3" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
         <is>
           <t>Zones de baignade et zones réglementaires</t>
         </is>
       </c>
-      <c r="B26" s="3" t="inlineStr">
+      <c r="B28" s="3" t="inlineStr">
         <is>
           <t>Aucune</t>
         </is>
       </c>
-      <c r="C26" s="3" t="inlineStr">
+      <c r="C28" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D26" s="3" t="n"/>
-      <c r="E26" s="3" t="inlineStr">
+      <c r="D28" s="3" t="n"/>
+      <c r="E28" s="3" t="inlineStr">
         <is>
           <t>Ce qui ne va pas : ligne « à venir » dans la légende, grisée et non sélectionnable. Aucune source n'est identifiée pour représenter ces zones ni les reconnaître au clic.
 Ce qu'il faut : identifier une source pour chacune des deux.</t>
         </is>
       </c>
-      <c r="F26" s="3" t="inlineStr">
+      <c r="F28" s="3" t="inlineStr">
         <is>
           <t>Aucune source confirmée. Pistes non vérifiées : données de baignade publiées par les communes ou les ARS, arrêtés préfectoraux à demander aux DDTM/DM.</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="5" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>Légende : vert = données fonctionnelles ; jaune = données simulées ; sans couleur = à compléter.</t>
-        </is>
-      </c>
-    </row>
     <row r="29">
-      <c r="A29" s="5" t="inlineStr">
-        <is>
-          <t>Méthode (21/09/2026) : les fiches de jeux de données ont été ouvertes et lues ; les services WMS/WFS et les fichiers n'ont pas été interrogés ni téléchargés. « Titre repéré, non ouvert » = trouvé par recherche seulement.</t>
-        </is>
-      </c>
+      <c r="A29" s="5" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>Légende : vert = données fonctionnelles ; jaune = données simulées ; sans couleur = à compléter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>Méthode (21/09/2026) : les fiches de jeux de données ont été ouvertes et lues ; les services WMS/WFS et les fichiers n'ont pas été interrogés ni téléchargés. « Titre repéré, non ouvert » = trouvé par recherche seulement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
         <is>
           <t>Le document de capacités WFS et WMTS de la Géoplateforme a été interrogé dans un navigateur le 21/09/2026 : les noms de couches patrinat_* cités ici y figurent. Aucune requête de données (GetFeature) n'a encore été testée.</t>
         </is>
@@ -1296,7 +1380,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C50"/>
+  <dimension ref="A1:C58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -2151,6 +2235,142 @@
       <c r="C50" s="7" t="inlineStr">
         <is>
           <t>Testée le 25/09/2026 : injoignable depuis l'extérieur (échec de connexion, domaine RIE), non ouverte avec succès — champ url_v2 du jeu de données, inutilisable pour un contact public</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="7" t="inlineStr">
+        <is>
+          <t>Limite terre-mer (verdict terre/mer au clic)</t>
+        </is>
+      </c>
+      <c r="B51" s="8" t="inlineStr">
+        <is>
+          <t>https://services.data.shom.fr/INSPIRE/wfs?service=WFS&amp;version=2.0.0&amp;request=GetCapabilities</t>
+        </is>
+      </c>
+      <c r="C51" s="7" t="inlineStr">
+        <is>
+          <t>Document de capacités interrogé dans le navigateur le 12/10/2026 (182 types d'objets listés)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="7" t="inlineStr">
+        <is>
+          <t>Limite terre-mer (verdict terre/mer au clic)</t>
+        </is>
+      </c>
+      <c r="B52" s="8" t="inlineStr">
+        <is>
+          <t>https://services.data.shom.fr/geonetwork/INSPIRE?service=CSW&amp;version=2.0.2&amp;request=GetRecordById&amp;Id=BDML_LIMTM.xml</t>
+        </is>
+      </c>
+      <c r="C52" s="7" t="inlineStr">
+        <is>
+          <t>Métadonnée du produit lue en réel le 12/10/2026 (définition PHMA, lignage, licence)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="7" t="inlineStr">
+        <is>
+          <t>Limite terre-mer (verdict terre/mer au clic)</t>
+        </is>
+      </c>
+      <c r="B53" s="8" t="inlineStr">
+        <is>
+          <t>https://dx.doi.org/10.17183/LIMTM</t>
+        </is>
+      </c>
+      <c r="C53" s="7" t="inlineStr">
+        <is>
+          <t>DOI cité par la métadonnée, non ouvert</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="7" t="inlineStr">
+        <is>
+          <t>Limite terre-mer (verdict terre/mer au clic)</t>
+        </is>
+      </c>
+      <c r="B54" s="8" t="inlineStr">
+        <is>
+          <t>https://www.data.gouv.fr/datasets/limite-terre-mer-1</t>
+        </is>
+      </c>
+      <c r="C54" s="7" t="inlineStr">
+        <is>
+          <t>Page ouverte précédemment (21/09/2026) ; service désormais interrogé en réel</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="7" t="inlineStr">
+        <is>
+          <t>Nature du fond au clic (conseil d’ancrage)</t>
+        </is>
+      </c>
+      <c r="B55" s="8" t="inlineStr">
+        <is>
+          <t>https://dx.doi.org/10.17183/HOM_GEOL_NATURES_FOND_50</t>
+        </is>
+      </c>
+      <c r="C55" s="7" t="inlineStr">
+        <is>
+          <t>DOI cité par la métadonnée, non ouvert</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="7" t="inlineStr">
+        <is>
+          <t>Nature du fond au clic (conseil d’ancrage)</t>
+        </is>
+      </c>
+      <c r="B56" s="8" t="inlineStr">
+        <is>
+          <t>https://services.data.shom.fr/geonetwork/INSPIRE?service=CSW&amp;version=2.0.2&amp;request=GetRecordById&amp;Id=HOM_GEOL_NATURES_FOND_50.xml</t>
+        </is>
+      </c>
+      <c r="C56" s="7" t="inlineStr">
+        <is>
+          <t>Métadonnée lue en réel le 12/10/2026 (lignage : 45 cartes G, 1990-2023)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="7" t="inlineStr">
+        <is>
+          <t>Nature du fond au clic (conseil d’ancrage)</t>
+        </is>
+      </c>
+      <c r="B57" s="8" t="inlineStr">
+        <is>
+          <t>https://services.data.shom.fr/INSPIRE/wms/v?service=WMS&amp;version=1.3.0&amp;request=GetLegendGraphic&amp;format=image/png&amp;layer=NDF_BDD_WLD_WGS84G_WMS</t>
+        </is>
+      </c>
+      <c r="C57" s="7" t="inlineStr">
+        <is>
+          <t>Légende officielle ouverte et lue le 12/10/2026 : 33 libellés, source de la table</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="7" t="inlineStr">
+        <is>
+          <t>Nature du fond au clic (conseil d’ancrage)</t>
+        </is>
+      </c>
+      <c r="B58" s="8" t="inlineStr">
+        <is>
+          <t>https://amidomar.beta.gouv.fr/bien-mouiller--pr%C3%A9server-les-fonds-marins/</t>
+        </is>
+      </c>
+      <c r="C58" s="7" t="inlineStr">
+        <is>
+          <t>Page du site AMIDOMAR dont sont repris les conseils affichés</t>
         </is>
       </c>
     </row>

--- a/data/donnees_carte_amidomar.xlsx
+++ b/data/donnees_carte_amidomar.xlsx
@@ -567,12 +567,12 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Socle terre/eau (marais, plages, bâti)</t>
+          <t>Socle terre/eau (objets du fond Plan IGN)</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>OpenMapTiles via data.gouv.fr</t>
+          <t>IGN, Plan IGN via Carte Facile (source « plan_ign » de la carte fantôme)</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -583,14 +583,16 @@
       <c r="D3" s="3" t="inlineStr"/>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>Ce qui ne va pas : plus la seule source du verdict depuis le 12/10/2026 (v2.14). La lecture de la couleur du fond de carte reste la réponse instantanée et le repli quand le réseau manque, mais elle n'est plus décisive : un verdict « à terre » est arbitré par le trait terre-mer du Shom (ligne ci-dessous).
+          <t>Ce qui ne va pas : plus la seule source du verdict depuis le 12/10/2026 (v2.14). La lecture des objets et de la couleur du fond de carte reste la réponse instantanée et le repli quand le réseau manque, mais elle n'est plus décisive : un verdict « à terre » est arbitré par le trait terre-mer du Shom (ligne ci-dessous).
+Correction du 13/10/2026 (v2.17) : ce socle n'est PAS OpenMapTiles. La carte fantôme ne compte qu'une source, plan_ign, et la terre ordinaire n'y est pas un objet — un champ, une plage, une dune ou un bourg sans bâti au pixel cliqué ne portent aucun objet et ne sont qu'un aplat rgb(240,240,237). Le verdict est donc désormais fondé sur une preuve d'EAU (objet hydro_, ou couleur rgb(151,205,213)) et non sur la recherche d'objets de terre.
 Ce qu'il faut : décider, après la phase de test auprès des DDTM pilotes, si la carte fantôme peut être supprimée — elle coûte une seconde carte MapLibre invisible et son jeu de tuiles.</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
           <t>Résolu le 12/10/2026 par la Limite terre-mer du Shom, branchée au clic : voir la ligne « Limite terre-mer (verdict terre/mer au clic) » ci-dessous.
-Le trait de côte Histolitt (https://www.data.gouv.fr/datasets/trait-de-cote-histolitt) reste à réserver à l'outre-mer : la page recommande Limite terre-mer pour la métropole, et c'est bien le produit métropolitain qui est utilisé.</t>
+Le trait de côte Histolitt (https://www.data.gouv.fr/datasets/trait-de-cote-histolitt) reste à réserver à l'outre-mer : la page recommande Limite terre-mer pour la métropole, et c'est bien le produit métropolitain qui est utilisé.
+Relevés du 13/10/2026 sur la carte fantôme, à conserver comme référence : mer (zooms 6 à 14) = objet hydro_surf + rgb(151,205,213) ; estran de la baie de Somme = hydro_surf + ocs_ + rgb(192,229,219) ; champ, plage, dune et bourg = aucun objet + rgb(240,240,237).</t>
         </is>
       </c>
     </row>
@@ -607,7 +609,7 @@
       </c>
       <c r="C4" s="9" t="inlineStr">
         <is>
-          <t>WFS 2.0.0, GeoJSON, filtre INTERSECTS au point ; couche non affichée</t>
+          <t>WFS 2.0.0, GeoJSON, filtres INTERSECTS (au point) et DWITHIN (couverture, 5 km) au point ; couche non affichée</t>
         </is>
       </c>
       <c r="D4" s="9" t="inlineStr">
@@ -621,7 +623,7 @@
           <t>Branché le 12/10/2026 (v2.14). Couche LIMTM_2154_WFS:limite_terre_mer_france_metropolitaine_polygones, qui porte les SURFACES TERRESTRES : zéro objet renvoyé = point côté mer, estran compris. Le produit matérialise la laisse des plus hautes mers astronomiques (coefficient 120, météo normale), soit la limite du DPM naturel au sens de l'article L2111-4 du CGPPP, à 1 à 5 m de résolution.
 Testé en réel le 12/10/2026 depuis le navigateur, sur quatre points : anse de Pen Hat et rade d'Hyères renvoient « mer », le bourg de Camaret renvoie « terre » avec numdep = 29, et l'estran de la baie du Mont-Saint-Michel (+13 m au-dessus du niveau de référence) renvoie bien « mer ». Réponses de 56 à 207 ms, 150 à 300 octets.
 Attention : la couche est en Lambert 93, le préfixe SRID=4326; du filtre est obligatoire — sans lui le service renvoie zéro objet, ce qui se lirait à tort comme « en mer ».
-Limites connues : France métropolitaine seulement (hors métropole, repli sur la détection locale) ; millésime 2021 ; produit « non certifié pour la navigation ». Licence Ouverte 2.0, citation obligatoire « Shom-IGN, 2021. https://dx.doi.org/10.17183/LIMTM », portée par l'attribution de la carte.
+Limites connues : France métropolitaine seulement (hors métropole, repli sur la détection locale) ; COUVERTURE DÉPARTEMENTALE, établie le 13/10/2026 — la couche ne couvre que les départements littoraux, mais les couvre entièrement jusqu'à leur limite intérieure (Vire, Falaise, Lisieux en 14, Évreux en 27, Rennes en 35 renvoient 1 objet ; Argentan en 61, Laval en 53, Niort en 79, Paris et Lyon renvoient 0). « Zéro objet » ne vaut donc pas « mer » partout : depuis la v2.17, une seconde requête DWITHIN de 5 km, lancée en parallèle, distingue « mer » de « hors couverture » (rayon calibré sur relevés réels : 10 et 20 km rattrapaient Niort, Argentan et Laval) ; millésime 2021 ; produit « non certifié pour la navigation ». Licence Ouverte 2.0, citation obligatoire « Shom-IGN, 2021. https://dx.doi.org/10.17183/LIMTM », portée par l'attribution de la carte.
 Reste à faire : le rattachement d'un point EN MER à une DDTM n'est pas couvert (numdep n'existe que pour les points à terre, et le Shom ne diffuse que des lignes de limites administratives, pas des polygones) — question reposée au Shom.</t>
         </is>
       </c>
@@ -1408,7 +1410,7 @@
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>Socle terre/eau (marais, plages, bâti)</t>
+          <t>Socle terre/eau (objets du fond Plan IGN)</t>
         </is>
       </c>
       <c r="B2" s="8" t="inlineStr">
@@ -1425,7 +1427,7 @@
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>Socle terre/eau (marais, plages, bâti)</t>
+          <t>Socle terre/eau (objets du fond Plan IGN)</t>
         </is>
       </c>
       <c r="B3" s="8" t="inlineStr">

--- a/data/donnees_carte_amidomar.xlsx
+++ b/data/donnees_carte_amidomar.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -45,6 +45,13 @@
       <color rgb="000563C1"/>
       <sz val="10"/>
       <u val="single"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="10"/>
+      <sz val="12"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="7">
@@ -105,10 +112,11 @@
       </bottom>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -132,9 +140,14 @@
     <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -1009,35 +1022,39 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+      <c r="A18" s="11" t="inlineStr">
         <is>
           <t>Cultures marines</t>
         </is>
       </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>data/cultures-marines.geojson</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>GeoJSON, 1 polygone fictif</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="inlineStr"/>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>données simulées</t>
-        </is>
-      </c>
-      <c r="F18" s="4" t="inlineStr">
-        <is>
-          <t>Aucun cadastre conchylicole national trouvé : il se récupère département par département.
-Manche (DDTM 50, shapefile, WMS/WFS, 2025) : https://www.data.gouv.fr/datasets/cadastre-conchylicole-1
-Charente-Maritime : https://www.data.gouv.fr/datasets/cadastre-conchylicole-en-charente-maritime
-Morbihan (entités linéaires) : https://www.data.gouv.fr/datasets/entites-lineaires-du-cadastre-conchylicole-du-departement-du-morbihan-1
-Ille-et-Vilaine (pêcheries) : https://www.data.gouv.fr/en/datasets/pecheries-issues-du-cadastre-conchylicole-dille-et-vilaine-35/
-À ne pas confondre : les zones de production conchylicole (GeoJSON, WFS, France métropolitaine) sont des zones de classement sanitaire, pas des concessions : https://www.data.gouv.fr/datasets/zones-de-production-ou-de-parcage-conchylicole-metropole</t>
+      <c r="B18" s="11" t="inlineStr">
+        <is>
+          <t>Cadastre conchylicole des DDTM, via GéoIDE (ogc.geo-ide.developpement-durable.gouv.fr) — Licence ouverte 2.0</t>
+        </is>
+      </c>
+      <c r="C18" s="11" t="inlineStr">
+        <is>
+          <t>WFS 2.0.0 (GML, filtre BBOX au point) pour l'interrogation, WMS 1.3.0 (EPSG:3857, PNG) pour l'affichage ; quatre flux sous une seule case de légende</t>
+        </is>
+      </c>
+      <c r="D18" s="11" t="n"/>
+      <c r="E18" s="11" t="inlineStr">
+        <is>
+          <t>Ce qui ne va pas : la couverture n'est pas nationale. Seuls trois départements publient leur cadastre sous une forme interrogeable — Finistère (1 406 parcelles, mise à jour juin 2026), Ille-et-Vilaine (2 194, mars 2024), Charente-Maritime (13 391 surfaciques et 1 254 linéaires, février 2023). Mesuré le 13/10/2026.
+Manche (50) : le flux répond au GetCapabilities mais tout GetFeature plante (« Encoding not supported by libiconv (8859part1) ») — bug serveur à signaler à la DDTM 50, le département s'ajouterait ensuite en une ligne.
+Morbihan (56, mis à jour avril 2026), Vendée (85), Loire-Atlantique (44), Gironde (33) : fichier à télécharger seulement, aucun flux.
+Ce qu'il faut : obtenir la publication d'un flux auprès de ces DDTM, ou héberger leurs fichiers convertis dans data/ et les remettre à jour à la main.</t>
+        </is>
+      </c>
+      <c r="F18" s="11" t="inlineStr">
+        <is>
+          <t>Branché le 13/10/2026 (v2.18), en remplacement d'un polygone FICTIF en rade d'Hyères qui portait seul la règle bloquante jusque-là (fichier data/cultures-marines.geojson supprimé).
+Couches : L_CADASTRE_CONCHYLICOLE_S_029, L_CADASTRE_CONCHYLICOLE_S_035, L_CADASTRE_CONCH_S_017 et L_CADASTRE_CONCH_L_017. Champs lus : CM1PAR (n° de parcelle), COMMUNE et ESPECE (COMMUNE absent en Charente-Maritime). Les flux portent aussi SURFACE_M2, DATE_EXPIR, ETAT, FAMILLE_EX, NATURE_JUR et l'auteur (ex. DDTM29/DML/SL/UCM) : non exploités à ce stade.
+Pièges vérifiés : en WFS 1.1.0 + EPSG:4326 la BBOX attend latitude puis longitude ; MapServer ne gère pas CQL_FILTER et renvoie une erreur sur outputFormat=application/json. Un ExceptionReport arrive en HTTP 200 et doit être traité comme une panne, pas comme une absence de parcelle.
+Latences mesurées : 147 ms sans parcelle, 736 ms au premier appel sur une parcelle.
+ÉCARTÉ, et pourquoi : le cadastre aquacole national du Cerema (https://www.data.gouv.fr/datasets/cadastre-aquacole-national) est la version harmonisée des mêmes fichiers DDTM — 37 612 parcelles, soit 50 fois la couche « fermes marines » du Shom (747) — mais son service ne renvoie aucun en-tête CORS (inappelable depuis un navigateur), ne renvoie aucune géométrie, et n'expose ni WMS ni WFS. Le flux WMS national de Géolittoral ne contient pas le cadastre. Le fichier cadastre_2026.zip reste téléchargeable sur Géolittoral si l'on choisit un jour de l'héberger.
+ÉCARTÉ aussi : la couche MARCUL du Shom (fermes marines) — ce sont les installations portées sur la carte marine, sans nom de parcelle, et non le cadastre administratif.
+Piste non explorée : les pêcheries d'Ille-et-Vilaine (ms:L_PECHERIES_L_035, même plateforme) sont aussi des occupations du DPM.</t>
         </is>
       </c>
     </row>
@@ -1382,7 +1399,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C58"/>
+  <dimension ref="A1:C66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -2373,6 +2390,142 @@
       <c r="C58" s="7" t="inlineStr">
         <is>
           <t>Page du site AMIDOMAR dont sont repris les conseils affichés</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="7" t="inlineStr">
+        <is>
+          <t>Cultures marines</t>
+        </is>
+      </c>
+      <c r="B59" s="12" t="inlineStr">
+        <is>
+          <t>https://www.data.gouv.fr/datasets/cadastre-conchylicole-du-finistere</t>
+        </is>
+      </c>
+      <c r="C59" s="7" t="inlineStr">
+        <is>
+          <t>Flux WFS et WMS réellement interrogés le 13/10/2026 : 1 406 parcelles, clic testé sur la parcelle MX01000956 (Locquénolé, Taulé)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="7" t="inlineStr">
+        <is>
+          <t>Cultures marines</t>
+        </is>
+      </c>
+      <c r="B60" s="12" t="inlineStr">
+        <is>
+          <t>https://www.data.gouv.fr/datasets/cadastre-conchylicole-ille-et-vilaine-35</t>
+        </is>
+      </c>
+      <c r="C60" s="7" t="inlineStr">
+        <is>
+          <t>Flux WFS interrogé le 13/10/2026 : 2 194 parcelles, GetFeature fonctionnel</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="7" t="inlineStr">
+        <is>
+          <t>Cultures marines</t>
+        </is>
+      </c>
+      <c r="B61" s="12" t="inlineStr">
+        <is>
+          <t>https://www.data.gouv.fr/datasets/cadastre-conchylicole-en-charente-maritime-representation-surfacique</t>
+        </is>
+      </c>
+      <c r="C61" s="7" t="inlineStr">
+        <is>
+          <t>Flux WFS interrogé le 13/10/2026 : 13 391 parcelles (la représentation linéaire en compte 1 254)</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="7" t="inlineStr">
+        <is>
+          <t>Cultures marines</t>
+        </is>
+      </c>
+      <c r="B62" s="12" t="inlineStr">
+        <is>
+          <t>https://www.data.gouv.fr/datasets/cadastre-conchylicole-1</t>
+        </is>
+      </c>
+      <c r="C62" s="7" t="inlineStr">
+        <is>
+          <t>DDTM Manche : flux interrogé le 13/10/2026, GetCapabilities OK mais GetFeature en panne (encodage 8859part1) — inutilisable en l'état</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="7" t="inlineStr">
+        <is>
+          <t>Cultures marines</t>
+        </is>
+      </c>
+      <c r="B63" s="12" t="inlineStr">
+        <is>
+          <t>https://www.data.gouv.fr/datasets/entites-surfaciques-du-cadastre-conchylicole-du-departement-du-morbihan</t>
+        </is>
+      </c>
+      <c r="C63" s="7" t="inlineStr">
+        <is>
+          <t>DDTM Morbihan, mis à jour le 16/04/2026 : page ouverte, aucun flux proposé (téléchargement seulement)</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="7" t="inlineStr">
+        <is>
+          <t>Cultures marines</t>
+        </is>
+      </c>
+      <c r="B64" s="12" t="inlineStr">
+        <is>
+          <t>https://www.data.gouv.fr/datasets/cadastre-aquacole-national</t>
+        </is>
+      </c>
+      <c r="C64" s="7" t="inlineStr">
+        <is>
+          <t>Cadastre national harmonisé du Cerema : service interrogé le 13/10/2026 (37 612 parcelles) mais sans en-tête CORS, donc inappelable depuis la carte</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="7" t="inlineStr">
+        <is>
+          <t>Cultures marines</t>
+        </is>
+      </c>
+      <c r="B65" s="12" t="inlineStr">
+        <is>
+          <t>https://www.geolittoral.developpement-durable.gouv.fr/telechargement-et-flux-de-donnees-a802.html</t>
+        </is>
+      </c>
+      <c r="C65" s="7" t="inlineStr">
+        <is>
+          <t>Page de téléchargement et flux de Géolittoral, ouverte le 13/10/2026 : fichiers cadastre_2026.zip et cadastre_emprise_2026.zip, et flux WMS national (qui ne contient pas le cadastre)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="7" t="inlineStr">
+        <is>
+          <t>Cultures marines</t>
+        </is>
+      </c>
+      <c r="B66" s="12" t="inlineStr">
+        <is>
+          <t>https://sextant.ifremer.fr/geonetwork/srv/api/records/98a7c90e-33c8-44bc-a27a-9b7b61ae829f</t>
+        </is>
+      </c>
+      <c r="C66" s="7" t="inlineStr">
+        <is>
+          <t>Fiche de métadonnées du cadastre aquacole national, lue le 13/10/2026 : producteur Cerema Géolittoral, données fournies par les DDTM</t>
         </is>
       </c>
     </row>
@@ -2426,6 +2579,14 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B47" r:id="rId46"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B48" r:id="rId47"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B59" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B60" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B61" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B62" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B63" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B64" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B65" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B66" r:id="rId56"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/donnees_carte_amidomar.xlsx
+++ b/data/donnees_carte_amidomar.xlsx
@@ -622,7 +622,7 @@
       </c>
       <c r="C4" s="9" t="inlineStr">
         <is>
-          <t>WFS 2.0.0, GeoJSON, filtres INTERSECTS (au point) et DWITHIN (couverture, 5 km) au point ; couche non affichée</t>
+          <t>WFS 2.0.0, GeoJSON, filtres INTERSECTS (au point) et DWITHIN (couverture, 20 km) au point ; couche non affichée</t>
         </is>
       </c>
       <c r="D4" s="9" t="inlineStr">
@@ -636,7 +636,7 @@
           <t>Branché le 12/10/2026 (v2.14). Couche LIMTM_2154_WFS:limite_terre_mer_france_metropolitaine_polygones, qui porte les SURFACES TERRESTRES : zéro objet renvoyé = point côté mer, estran compris. Le produit matérialise la laisse des plus hautes mers astronomiques (coefficient 120, météo normale), soit la limite du DPM naturel au sens de l'article L2111-4 du CGPPP, à 1 à 5 m de résolution.
 Testé en réel le 12/10/2026 depuis le navigateur, sur quatre points : anse de Pen Hat et rade d'Hyères renvoient « mer », le bourg de Camaret renvoie « terre » avec numdep = 29, et l'estran de la baie du Mont-Saint-Michel (+13 m au-dessus du niveau de référence) renvoie bien « mer ». Réponses de 56 à 207 ms, 150 à 300 octets.
 Attention : la couche est en Lambert 93, le préfixe SRID=4326; du filtre est obligatoire — sans lui le service renvoie zéro objet, ce qui se lirait à tort comme « en mer ».
-Limites connues : France métropolitaine seulement (hors métropole, repli sur la détection locale) ; COUVERTURE DÉPARTEMENTALE, établie le 13/10/2026 — la couche ne couvre que les départements littoraux, mais les couvre entièrement jusqu'à leur limite intérieure (Vire, Falaise, Lisieux en 14, Évreux en 27, Rennes en 35 renvoient 1 objet ; Argentan en 61, Laval en 53, Niort en 79, Paris et Lyon renvoient 0). « Zéro objet » ne vaut donc pas « mer » partout : depuis la v2.17, une seconde requête DWITHIN de 5 km, lancée en parallèle, distingue « mer » de « hors couverture » (rayon calibré sur relevés réels : 10 et 20 km rattrapaient Niort, Argentan et Laval) ; millésime 2021 ; produit « non certifié pour la navigation ». Licence Ouverte 2.0, citation obligatoire « Shom-IGN, 2021. https://dx.doi.org/10.17183/LIMTM », portée par l'attribution de la carte.
+Limites connues : France métropolitaine seulement (hors métropole, repli sur la détection locale) ; COUVERTURE DÉPARTEMENTALE, établie le 13/10/2026 — la couche ne couvre que les départements littoraux, mais les couvre entièrement jusqu'à leur limite intérieure (Vire, Falaise, Lisieux en 14, Évreux en 27, Rennes en 35 renvoient 1 objet ; Argentan en 61, Laval en 53, Niort en 79, Paris et Lyon renvoient 0). « Zéro objet » ne vaut donc pas « mer » partout : depuis la v2.17, une seconde requête DWITHIN, lancée en parallèle, distingue « mer » de « hors couverture ». RAYON PORTÉ DE 5 À 20 KM LE 14/10/2026 : à 5 km, un clic sur l'estran de la baie du Mont-Saint-Michel produisait un faux « vous êtes à terre » (8 échecs sur 24 points tirés au hasard dans la baie, alors que le Shom répondait « mer » 24 fois sur 24) — à marée basse le point est à plus de 5 km de toute terre cartographiée. Aucun rayon ne sépare proprement les deux cas : la mer en exige au moins 20 km, les villes de l'intérieur moins de 10. 20 km est retenu pour ne jamais bloquer une étendue d'eau légitime ; Niort, Argentan et Laval ne sont donc plus avertis, Paris, Lyon, Le Mans, Poitiers, Chartres, Alençon et Angers le restent. Piste pour supprimer ce compromis : résoudre le département du point via ADMINEXPRESS (Géoplateforme) au lieu de raisonner en distance ; millésime 2021 ; produit « non certifié pour la navigation ». Licence Ouverte 2.0, citation obligatoire « Shom-IGN, 2021. https://dx.doi.org/10.17183/LIMTM », portée par l'attribution de la carte.
 Reste à faire : le rattachement d'un point EN MER à une DDTM n'est pas couvert (numdep n'existe que pour les points à terre, et le Shom ne diffuse que des lignes de limites administratives, pas des polygones) — question reposée au Shom.</t>
         </is>
       </c>

--- a/data/donnees_carte_amidomar.xlsx
+++ b/data/donnees_carte_amidomar.xlsx
@@ -1054,7 +1054,8 @@
 Latences mesurées : 147 ms sans parcelle, 736 ms au premier appel sur une parcelle.
 ÉCARTÉ, et pourquoi : le cadastre aquacole national du Cerema (https://www.data.gouv.fr/datasets/cadastre-aquacole-national) est la version harmonisée des mêmes fichiers DDTM — 37 612 parcelles, soit 50 fois la couche « fermes marines » du Shom (747) — mais son service ne renvoie aucun en-tête CORS (inappelable depuis un navigateur), ne renvoie aucune géométrie, et n'expose ni WMS ni WFS. Le flux WMS national de Géolittoral ne contient pas le cadastre. Le fichier cadastre_2026.zip reste téléchargeable sur Géolittoral si l'on choisit un jour de l'héberger.
 ÉCARTÉ aussi : la couche MARCUL du Shom (fermes marines) — ce sont les installations portées sur la carte marine, sans nom de parcelle, et non le cadastre administratif.
-Piste non explorée : les pêcheries d'Ille-et-Vilaine (ms:L_PECHERIES_L_035, même plateforme) sont aussi des occupations du DPM.</t>
+Piste non explorée : les pêcheries d'Ille-et-Vilaine (ms:L_PECHERIES_L_035, même plateforme) sont aussi des occupations du DPM.
+v2.21 (14/10/2026) : la carte ne se contente plus d'un oui/non — elle lit la géométrie renvoyée et mesure la distance à la parcelle la plus proche. Blocage à 5 m ou à l'intérieur du polygone, simple signalement jusqu'à 40 m. Vérifié le 14/10/2026 : MapServer filtre sur la géométrie réelle et non sur le rectangle englobant, ce qui est indispensable pour les bouchots de la baie du Mont-Saint-Michel, bandes diagonales dont le rectangle englobant couvre les couloirs entre parcelles.</t>
         </is>
       </c>
     </row>

--- a/data/donnees_carte_amidomar.xlsx
+++ b/data/donnees_carte_amidomar.xlsx
@@ -510,7 +510,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:F34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1365,25 +1365,81 @@
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="5" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="5" t="inlineStr">
-        <is>
-          <t>Légende : vert = données fonctionnelles ; jaune = données simulées ; sans couleur = à compléter.</t>
+    <row r="29" ht="150" customHeight="1">
+      <c r="A29" s="9" t="inlineStr">
+        <is>
+          <t>Rattachement départemental au clic (quelle DDTM ?)</t>
+        </is>
+      </c>
+      <c r="B29" s="9" t="inlineStr">
+        <is>
+          <t>SHOM-IGN, LIMTM 2021, services INSPIRE — attribut numdep de la couche limite_terre_mer_france_metropolitaine_polygones</t>
+        </is>
+      </c>
+      <c r="C29" s="9" t="inlineStr">
+        <is>
+          <t>WFS 2.0.0, GeoJSON, filtre DWITHIN à rayons progressifs (1, 2, 5, 10 km)</t>
+        </is>
+      </c>
+      <c r="D29" s="9" t="inlineStr">
+        <is>
+          <t>données fonctionnelles</t>
+        </is>
+      </c>
+      <c r="E29" s="9" t="inlineStr"/>
+      <c r="F29" s="9" t="inlineStr">
+        <is>
+          <t>Branché le 14/10/2026 (v2.22), sans nouvelle source : la couche était déjà interrogée depuis la v2.14 et renvoyait déjà numdep. Calibrage vérifié en réel le 14/10/2026 sur 6 points (rade de Brest 29, golfe du Morbihan 56, rade de Toulon 83, Les Sept-Îles 22, baie de Saint-Brieuc 22) : réponse univoque à chaque fois. LIMITE À CONNAÎTRE : la couche porte des surfaces TERRESTRES, le département est donc celui de la côte la plus proche, jamais celui du point cliqué — c'est une inférence, et aucune limite départementale ne s'étend en mer dans ce jeu. Piste pour lever cette limite : demander au Shom (Eric Le Guen, équipe zones et limites maritimes) s'il existe un référentiel de limites administratives EN MER diffusable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="150" customHeight="1">
+      <c r="A30" s="11" t="inlineStr">
+        <is>
+          <t>Messages d'orientation par DDTM (règles locales)</t>
+        </is>
+      </c>
+      <c r="B30" s="11" t="inlineStr">
+        <is>
+          <t>data/ddtm-messages.json — rédigé par l'équipe, en attendant l'interface instructeur Grist</t>
+        </is>
+      </c>
+      <c r="C30" s="11" t="inlineStr">
+        <is>
+          <t>JSON, texte brut échappé à l'affichage, 2 fiches (22 et 83)</t>
+        </is>
+      </c>
+      <c r="D30" s="11" t="inlineStr"/>
+      <c r="E30" s="11" t="inlineStr">
+        <is>
+          <t>Ce qui ne va pas : les zones dédiées du Var (83) ne sont pas renseignées — 4 entrées « À COMPLÉTER ». Le drapeau brouillon est posé et la carte affiche « information provisoire », mais ces zones doivent être obtenues auprès de la DDTM 83 avant toute communication publique. Le 29 et le 56 n'ont pas de message, ce qui est normal à ce jour.</t>
+        </is>
+      </c>
+      <c r="F30" s="11" t="inlineStr">
+        <is>
+          <t>Fichier PROVISOIRE par conception : il sera régénéré depuis la table DDTM de Grist quand l'interface instructeur permettra aux agents de gérer leurs bandeaux par périmètre en autonomie. Ses noms de champs sont déjà ceux prévus pour cette table (ddtm, message_titre, message_consequence, message_detail, liste, lien, libelle_lien), pour que le basculement soit un script d'export et non une réécriture de la carte. Secours hors ligne volontairement vide.</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>Méthode (21/09/2026) : les fiches de jeux de données ont été ouvertes et lues ; les services WMS/WFS et les fichiers n'ont pas été interrogés ni téléchargés. « Titre repéré, non ouvert » = trouvé par recherche seulement.</t>
-        </is>
-      </c>
+      <c r="A31" s="5" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>Légende : vert = données fonctionnelles ; jaune = données simulées ; sans couleur = à compléter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>Méthode (21/09/2026) : les fiches de jeux de données ont été ouvertes et lues ; les services WMS/WFS et les fichiers n'ont pas été interrogés ni téléchargés. « Titre repéré, non ouvert » = trouvé par recherche seulement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
         <is>
           <t>Le document de capacités WFS et WMTS de la Géoplateforme a été interrogé dans un navigateur le 21/09/2026 : les noms de couches patrinat_* cités ici y figurent. Aucune requête de données (GetFeature) n'a encore été testée.</t>
         </is>

--- a/data/donnees_carte_amidomar.xlsx
+++ b/data/donnees_carte_amidomar.xlsx
@@ -510,7 +510,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F34"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1393,7 +1393,7 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="150" customHeight="1">
+    <row r="30" ht="190" customHeight="1">
       <c r="A30" s="11" t="inlineStr">
         <is>
           <t>Messages d'orientation par DDTM (règles locales)</t>
@@ -1406,40 +1406,68 @@
       </c>
       <c r="C30" s="11" t="inlineStr">
         <is>
-          <t>JSON, texte brut échappé à l'affichage, 2 fiches (22 et 83)</t>
+          <t>JSON, texte brut échappé à l'affichage, 2 fiches (22 et 83), 5 zones listées pour le 83</t>
         </is>
       </c>
       <c r="D30" s="11" t="inlineStr"/>
       <c r="E30" s="11" t="inlineStr">
         <is>
-          <t>Ce qui ne va pas : les zones dédiées du Var (83) ne sont pas renseignées — 4 entrées « À COMPLÉTER ». Le drapeau brouillon est posé et la carte affiche « information provisoire », mais ces zones doivent être obtenues auprès de la DDTM 83 avant toute communication publique. Le 29 et le 56 n'ont pas de message, ce qui est normal à ce jour.</t>
+          <t>Ce qui ne va pas : la liste des zones du Var est partielle. Les 5 zones reçues de la DDTM 83 (cartes PDF n°41 Les Canebiers et n°42 La Bouillabaisse, octobre 2022) sont toutes sur la commune de Saint-Tropez, alors que la DDTM 83 couvre toute la façade varoise. Le texte de la carte l'annonce et le drapeau brouillon reste posé, mais il faut obtenir les zones des autres communes (Hyères, Giens, Porquerolles, Cavalaire, Le Lavandou, Bandol...). Le 29 et le 56 n'ont pas de message, ce qui est normal à ce jour.</t>
         </is>
       </c>
       <c r="F30" s="11" t="inlineStr">
         <is>
-          <t>Fichier PROVISOIRE par conception : il sera régénéré depuis la table DDTM de Grist quand l'interface instructeur permettra aux agents de gérer leurs bandeaux par périmètre en autonomie. Ses noms de champs sont déjà ceux prévus pour cette table (ddtm, message_titre, message_consequence, message_detail, liste, lien, libelle_lien), pour que le basculement soit un script d'export et non une réécriture de la carte. Secours hors ligne volontairement vide.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="n"/>
+          <t>Fichier PROVISOIRE par conception : il sera régénéré depuis la table DDTM de Grist quand l'interface instructeur permettra aux agents de gérer leurs bandeaux par périmètre en autonomie. Ses noms de champs sont déjà ceux prévus pour cette table. PISTE NON ENGAGÉE : les deux cartes PDF donnent les 4 sommets GPS de chaque zone (degrés-minutes décimales). Les convertir en polygones GeoJSON permettrait de répondre directement à la question de l'usager (« mon emplacement est-il dans une zone autorisée ? ») au lieu de lui faire lire une liste de noms, et d'afficher les zones sur la carte comme les ZMEL. Secours hors ligne volontairement vide.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="190" customHeight="1">
+      <c r="A31" s="11" t="inlineStr">
+        <is>
+          <t>Zones de mouillage autorisées (AOT)</t>
+        </is>
+      </c>
+      <c r="B31" s="11" t="inlineStr">
+        <is>
+          <t>data/zones-aot.geojson — relevé manuel sur les cartes PDF n°41 et n°42 de la DDTM du Var / SML-BLO, octobre 2022</t>
+        </is>
+      </c>
+      <c r="C31" s="11" t="inlineStr">
+        <is>
+          <t>GeoJSON, 5 polygones (4 sommets chacun), propriétés : ddtm, commune, lieu, zone, capacité, exposition, profondeur</t>
+        </is>
+      </c>
+      <c r="D31" s="11" t="inlineStr"/>
+      <c r="E31" s="11" t="inlineStr">
+        <is>
+          <t>Ce qui ne va pas : couverture très partielle (5 zones, commune de Saint-Tropez uniquement) et saisie non validée. Les coordonnées ont été lues à l'oeil sur des PDF : une erreur déplacerait une limite réglementaire. Il faut (1) faire confirmer les sommets par la DDTM 83, (2) vérifier que les cartes d'octobre 2022 sont toujours en vigueur, (3) obtenir les zones des autres communes varoises.</t>
+        </is>
+      </c>
+      <c r="F31" s="11" t="inlineStr">
+        <is>
+          <t>Contrôle de cohérence déjà fait : surface du polygone divisée par la capacité annoncée = 937, 1016, 863, 914 et 1065 m2 par mouillage sur les cinq zones, soit environ 18 m de rayon d'évitage. Cette convergence écarte la faute de frappe mais ne vaut pas validation. Le fichier sert deux fois : couche cartographique (id zones_aot) et liste cliquable du message DDTM, reliées par la propriété ddtm. Demander à la DDTM 83 un export SIG plutôt que des PDF pour les prochaines communes.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" s="5" t="inlineStr">
-        <is>
-          <t>Légende : vert = données fonctionnelles ; jaune = données simulées ; sans couleur = à compléter.</t>
-        </is>
-      </c>
+      <c r="A32" s="5" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>Méthode (21/09/2026) : les fiches de jeux de données ont été ouvertes et lues ; les services WMS/WFS et les fichiers n'ont pas été interrogés ni téléchargés. « Titre repéré, non ouvert » = trouvé par recherche seulement.</t>
+          <t>Légende : vert = données fonctionnelles ; jaune = données simulées ; sans couleur = à compléter.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>Méthode (21/09/2026) : les fiches de jeux de données ont été ouvertes et lues ; les services WMS/WFS et les fichiers n'ont pas été interrogés ni téléchargés. « Titre repéré, non ouvert » = trouvé par recherche seulement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
         <is>
           <t>Le document de capacités WFS et WMTS de la Géoplateforme a été interrogé dans un navigateur le 21/09/2026 : les noms de couches patrinat_* cités ici y figurent. Aucune requête de données (GetFeature) n'a encore été testée.</t>
         </is>

--- a/data/donnees_carte_amidomar.xlsx
+++ b/data/donnees_carte_amidomar.xlsx
@@ -510,7 +510,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:F34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1406,7 +1406,7 @@
       </c>
       <c r="C30" s="11" t="inlineStr">
         <is>
-          <t>JSON, texte brut échappé à l'affichage, 2 fiches (22 et 83), 5 zones listées pour le 83</t>
+          <t>JSON, texte brut échappé à l'affichage, 2 fiches (22 et 83). Le 83 porte deux jeux de textes : l'état par défaut et l'état « emplacement dans une zone autorisée » (champs *_zone, v2.24)</t>
         </is>
       </c>
       <c r="D30" s="11" t="inlineStr"/>
@@ -1421,53 +1421,25 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="190" customHeight="1">
-      <c r="A31" s="11" t="inlineStr">
-        <is>
-          <t>Zones de mouillage autorisées (AOT)</t>
-        </is>
-      </c>
-      <c r="B31" s="11" t="inlineStr">
-        <is>
-          <t>data/zones-aot.geojson — relevé manuel sur les cartes PDF n°41 et n°42 de la DDTM du Var / SML-BLO, octobre 2022</t>
-        </is>
-      </c>
-      <c r="C31" s="11" t="inlineStr">
-        <is>
-          <t>GeoJSON, 5 polygones (4 sommets chacun), propriétés : ddtm, commune, lieu, zone, capacité, exposition, profondeur</t>
-        </is>
-      </c>
-      <c r="D31" s="11" t="inlineStr"/>
-      <c r="E31" s="11" t="inlineStr">
-        <is>
-          <t>Ce qui ne va pas : couverture très partielle (5 zones, commune de Saint-Tropez uniquement) et saisie non validée. Les coordonnées ont été lues à l'oeil sur des PDF : une erreur déplacerait une limite réglementaire. Il faut (1) faire confirmer les sommets par la DDTM 83, (2) vérifier que les cartes d'octobre 2022 sont toujours en vigueur, (3) obtenir les zones des autres communes varoises.</t>
-        </is>
-      </c>
-      <c r="F31" s="11" t="inlineStr">
-        <is>
-          <t>Contrôle de cohérence déjà fait : surface du polygone divisée par la capacité annoncée = 937, 1016, 863, 914 et 1065 m2 par mouillage sur les cinq zones, soit environ 18 m de rayon d'évitage. Cette convergence écarte la faute de frappe mais ne vaut pas validation. Le fichier sert deux fois : couche cartographique (id zones_aot) et liste cliquable du message DDTM, reliées par la propriété ddtm. Demander à la DDTM 83 un export SIG plutôt que des PDF pour les prochaines communes.</t>
-        </is>
-      </c>
+    <row r="31">
+      <c r="A31" s="5" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="5" t="n"/>
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>Légende : vert = données fonctionnelles ; jaune = données simulées ; sans couleur = à compléter.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>Légende : vert = données fonctionnelles ; jaune = données simulées ; sans couleur = à compléter.</t>
+          <t>Méthode (21/09/2026) : les fiches de jeux de données ont été ouvertes et lues ; les services WMS/WFS et les fichiers n'ont pas été interrogés ni téléchargés. « Titre repéré, non ouvert » = trouvé par recherche seulement.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>Méthode (21/09/2026) : les fiches de jeux de données ont été ouvertes et lues ; les services WMS/WFS et les fichiers n'ont pas été interrogés ni téléchargés. « Titre repéré, non ouvert » = trouvé par recherche seulement.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="5" t="inlineStr">
         <is>
           <t>Le document de capacités WFS et WMTS de la Géoplateforme a été interrogé dans un navigateur le 21/09/2026 : les noms de couches patrinat_* cités ici y figurent. Aucune requête de données (GetFeature) n'a encore été testée.</t>
         </is>

--- a/data/donnees_carte_amidomar.xlsx
+++ b/data/donnees_carte_amidomar.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -52,6 +52,10 @@
       <color theme="10"/>
       <sz val="12"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="12"/>
     </font>
   </fonts>
   <fills count="7">
@@ -116,7 +120,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -144,6 +148,7 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -863,17 +868,20 @@
       <c r="D12" s="3" t="inlineStr"/>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Ce qui ne va pas : les herbiers n'apparaissent presque qu'en Occitanie (Palavas, Albères), nulle part ailleurs (Hyères, Corse, Quiberon, Brest, Arcachon). La légende annonce la zostère, absente de cette source.
-Ce qu'il faut : une source couvrant tout le littoral, avec les contours en données.</t>
+          <t>Ce qui ne va pas : la couche affichée (Ifremer) ne montre les herbiers presque qu'en Occitanie (Palavas, Albères), nulle part ailleurs (Hyères, Corse, Quiberon, Brest, Arcachon). La légende annonce la zostère, absente de cette source. La couche est décochée au chargement.
+Ce qu'il faut : brancher la source nationale de l'OFB, qualifiée et testée le 14/10/2026 — intégration ajournée le 15/10/2026, trois points de produit restant à trancher (quelle couche afficher, ce que dit le clic, si un herbier bloque). Voir data/SOURCES.md §4.</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>Inventaire national des herbiers de posidonie (OFB, polygones) : shapefile, WMS et WFS, Licence Ouverte 2.0, mis à jour en 2025-2026. À vérifier : la page indique un périmètre limité aux sites Natura 2000 marins, donc la couverture de Hyères et de la Corse est à contrôler. https://www.data.gouv.fr/datasets/inventaire-des-donnees-disponibles-spatialisant-les-herbiers-de-posidonie-en-france-metropolitaine-polygone
-Version posidonie et zostère : https://www.data.gouv.fr/datasets/inventaire-des-donnees-disponibles-spatialisant-les-herbiers-de-posidonie-et-de-zostere-en-france-metropolitaine
-Zostères 2024 (Zostera marina et noltei, trois façades) : https://data.ofb.fr/catalogue/srv/api/records/c6f8ddbc-a9d2-4563-8bba-cf45a6281400?language=fre
-Cartographie Toulon-Hyères (titre repéré, non ouvert) : https://sextant.ifremer.fr/geonetwork/srv/api/records/bf44e010-2354-11dd-aeec-000086f6a603
-Contact OFB : sig@ofb.gouv.fr. Le Géocatalogue (fiche « Herbiers de posidonie de Corse ») était fermé au moment du test.</t>
+          <t>Source retenue, vérifiée par requête réelle le 14/10/2026 depuis l'origine de déploiement : OFB / Life intégré Marha, https://wxs.ofb.fr/geoserver/habitat/wfs — Licence Ouverte Etalab 2.0, sans clé, CORS autorisé.
+La réserve précédente est levée : le périmètre n'est PAS limité aux sites Natura 2000. La couche habitat:eco_met_herbiers_emprise_simple_ofb_pol_3857 (« Nav&amp;Co ») couvre les trois façades — 3 527 polygones : posidonie 1 554, zostère marine 1 068, zostère naine 847. Testé : Hyères renvoie bien un polygone de posidonie (94 ms), le golfe du Morbihan une zostère naine (26 ms). Interrogation au point par INTERSECTS, attribut géométrique geom, préfixe SRID=4326; obligatoire.
+Elle embarque déjà le message usager (title, subtitle, et le lien vers l'arrêté PREMAR 123/2019), ce qui évite d'en rédiger un autre.
+Deux limites mesurées : pas de tuiles vectorielles (le serveur répond InvalidFormat), et cette couche-là n'est pas dans le cache WMTS — ce sont les couches détaillées qui le sont (eco_met_herbiers_2022_ofb_pol_3857, TileMatrixSet EPSG:900913). Le GeoJSON intégral fait 18,9 Mo, donc pas chargeable d'un bloc.
+Statut juridique : inventaire, NON opposable. Un polygone ne vaut pas constat, son absence ne vaut pas absence d'herbier.
+À demander à sig@ofb.gouv.fr : mise en cache WMTS de la couche Nav&amp;Co, projet éventuel de tuiles vectorielles, qui reprend l'actualisation après la fin du Life Marha au 31/12/2025, et accord pour reprendre les libellés.
+https://www.data.gouv.fr/datasets/inventaire-2024-dherbiers-de-zosteres-en-france-metropolitaine-polygone-1
+https://www.data.gouv.fr/datasets/inventaire-des-donnees-disponibles-spatialisant-les-herbiers-de-posidonie-en-france-metropolitaine-polygone</t>
         </is>
       </c>
     </row>
@@ -1456,7 +1464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C66"/>
+  <dimension ref="A1:C67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -1681,7 +1689,7 @@
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>Page ouverte (métadonnées lues, service non interrogé)</t>
+          <t>Page ouverte et service interrogé par requête réelle (14/10/2026)</t>
         </is>
       </c>
     </row>
@@ -1698,7 +1706,7 @@
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>Page ouverte (métadonnées lues, service non interrogé)</t>
+          <t>Page ouverte et service interrogé par requête réelle (14/10/2026)</t>
         </is>
       </c>
     </row>
@@ -1715,7 +1723,7 @@
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>Page ouverte (métadonnées lues, service non interrogé)</t>
+          <t>Page ouverte et service interrogé par requête réelle (14/10/2026)</t>
         </is>
       </c>
     </row>
@@ -2583,6 +2591,23 @@
       <c r="C66" s="7" t="inlineStr">
         <is>
           <t>Fiche de métadonnées du cadastre aquacole national, lue le 13/10/2026 : producteur Cerema Géolittoral, données fournies par les DDTM</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="7" t="inlineStr">
+        <is>
+          <t>Herbiers — service WFS de l'OFB</t>
+        </is>
+      </c>
+      <c r="B67" s="13" t="inlineStr">
+        <is>
+          <t>https://wxs.ofb.fr/geoserver/habitat/wfs?service=WFS&amp;version=2.0.0&amp;request=GetCapabilities</t>
+        </is>
+      </c>
+      <c r="C67" s="7" t="inlineStr">
+        <is>
+          <t>Service interrogé, 90 couches tuilées côté GeoWebCache (14-15/10/2026)</t>
         </is>
       </c>
     </row>

--- a/data/donnees_carte_amidomar.xlsx
+++ b/data/donnees_carte_amidomar.xlsx
@@ -1147,16 +1147,19 @@
       <c r="D21" s="3" t="inlineStr"/>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Ce qui ne va pas : branché en v2.6 (25/09/2026) et testé sur l'API réelle, mais le clic complet sur la carte publiée avec l'API réelle reste à vérifier ; la maille d'environ 115 m donne un fond moyen, peu fidèle près des roches et des chenaux.
-Ce qu'il faut : un test en conditions réelles sur la carte publiée, puis, si besoin, une bathymétrie plus fine sur les zones pilotes (MNT côtiers du Shom à 5-20 m).</t>
+          <t>Ce qui ne va pas : branchée en v2.6 (25/09/2026) et testée sur l'API réelle, mais le clic complet sur la carte publiée avec l'API réelle reste à vérifier ; la maille d'environ 115 m donne un fond moyen, peu fidèle près des roches et des chenaux. La profondeur n'est pas affichée à l'usager, et elle n'est demandée que si le point est à moins de 100 m d'une AOT.
+Ce qu'il faut : un test en conditions réelles sur la carte publiée ; afficher la profondeur dans la popup au-dessus de la nature du fond, avec la fourchette min/max et le millésime du levé ; trancher la valeur retenue pour le rayon d'évitage (min = prudence anti-collision, max = prudence anti-échouage, avg aujourd'hui).
+Arbitrage du 26/10/2026 : la carte doit porter les deux bornes de la marée (« 13,7 à 19,1 m selon la marée ») et non la seule sonde, sinon deux nombres distants du marnage cohabitent sans lien. En Méditerranée, pas de fourchette ni de mention de marée : la référence y est le niveau moyen.</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>API testée le 25/09/2026 depuis le site publié : CORS accepté, 60 à 370 ms ; Quiberon −12,35 m, Brest −23,6 m, Saint-Malo −1,86 m. https://rest.emodnet-bathymetry.eu/depth_sample?geom=POINT(-2.970485 47.510572)
-Écartés : WMS « MNT » du Shom non interrogeable au point (LayerNotQueryable), export image/x-bil incohérent (tests du 25/09/2026).
-Plus fin (non testé) : MNT côtiers du Shom à 5-20 m (Morbihan, Pertuis, Arcachon, Île de Ré, Gironde…) visibles dans le WMS INSPIRE, à télécharger et convertir : https://diffusion.shom.fr/donnees/bathymerie/mnt-bathymetriques.html
-MNT de façade Homonim (111 m, Licence Ouverte) : https://www.data.gouv.fr/datasets/mnt-bathymetrique-de-facade-atlantique-projet-homonim-1</t>
+          <t>API testée le 25/09/2026 depuis le site publié : CORS accepté, 60 à 370 ms ; Quiberon −12,35 m, Brest −23,6 m, Saint-Malo −1,86 m. Retestée le 15/10/2026 sur 7 sites de mouillage : 28 à 80 ms. https://rest.emodnet-bathymetry.eu/depth_sample?geom=POINT(-2.970485 47.510572)
+La réponse contient déjà min, max, stdev, elementarySurfaces et reference (identifiant du levé) — non lus par la carte aujourd'hui. Les 7 réponses portent organisation_id 540 = Shom (EDMO) : la source de vérité est le Shom, EMODnet en est le véhicule interrogeable. Au large de Saint-Malo la provenance est DTM_GNB_20m, soit le MNT côtier 20 m du golfe normand-breton du Shom lui-même.
+Écartés, définitivement (tests du 15/10/2026) : WMS « MNT » du Shom non interrogeable au point (LayerNotQueryable, sur requête complète) ; GeoTIFF renvoyé en RVBA 8 bits (SamplesPerPixel 4, photometric RGB) et image/x-bil = le pixel réinterprété en flottant, donc aucune valeur ; pas de WCS (404 sur 4 points d'entrée) ; GetLegendGraphic en 403.
+Plus fin : prépaquets Shom publics, sans clé — MNT côtier Morbihan 20 m = 101 Mio, MNT façade Atlantique 100 m = 442 Mio, en variantes PBMA (zéro hydrographique) et NM. Non retenu pour l'instant : chaîne de prétraitement + hébergement, contre la propriété « un seul fichier HTML ». Et là où le Shom a un MNT fin, EMODnet le sert déjà. https://services.data.shom.fr/INSPIRE/telechargement/prepackageGroup?request=GetCapabilities
+MNT de façade Homonim (Licence Ouverte) : https://www.data.gouv.fr/datasets/mnt-bathymetrique-de-facade-atlantique-projet-homonim-1
+Millésime du levé (nouveau, testé le 26/10/2026) : le Shom publie les emprises de ses levés bathymétriques en WFS, en quatre couches par période (LEVES_BATHY_AVANT_1970_WFS, _1970-1990_, _1990-2005_, _APRES_2005_ ; attribut géométrique « geometry »), avec sursta/surend (dates réelles), instrument, tecsou, sonde, zmin/zmax. 31 à 89 ms pour les quatre. La jointure avec EMODnet marche : id_md contient le code renvoyé dans reference.identifier. Piège : le code CDI ne porte PAS l'année du levé (S199206700 = levé de 1990-1991). https://services.data.shom.fr/static/specifications/Descriptif_Contenu_ProduitExterne_LEVES_BATHY.pdf</t>
         </is>
       </c>
     </row>
@@ -1464,7 +1467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C67"/>
+  <dimension ref="A1:C70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -2608,6 +2611,57 @@
       <c r="C67" s="7" t="inlineStr">
         <is>
           <t>Service interrogé, 90 couches tuilées côté GeoWebCache (14-15/10/2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="7" t="inlineStr">
+        <is>
+          <t>Profondeur au point (colonne d'eau à marée haute)</t>
+        </is>
+      </c>
+      <c r="B68" s="8" t="inlineStr">
+        <is>
+          <t>https://services.data.shom.fr/INSPIRE/telechargement/prepackageGroup?request=GetCapabilities</t>
+        </is>
+      </c>
+      <c r="C68" s="7" t="inlineStr">
+        <is>
+          <t>Service de prépaquets interrogé le 15/10/2026 : 119 ressources, public sans clé, Fees none ; poids des MNT mesurés par requête Range (HTTP 206)</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="7" t="inlineStr">
+        <is>
+          <t>Profondeur au point (colonne d'eau à marée haute)</t>
+        </is>
+      </c>
+      <c r="B69" s="8" t="inlineStr">
+        <is>
+          <t>https://edmo.seadatanet.org/report/540</t>
+        </is>
+      </c>
+      <c r="C69" s="7" t="inlineStr">
+        <is>
+          <t>Page ouverte le 15/10/2026 : EDMO 540 = Shom, confirme la provenance des valeurs EMODnet</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="7" t="inlineStr">
+        <is>
+          <t>Profondeur au point (colonne d'eau à marée haute)</t>
+        </is>
+      </c>
+      <c r="B70" s="8" t="inlineStr">
+        <is>
+          <t>https://services.data.shom.fr/static/specifications/Descriptif_Contenu_ProduitExterne_LEVES_BATHY.pdf</t>
+        </is>
+      </c>
+      <c r="C70" s="7" t="inlineStr">
+        <is>
+          <t>Spécification du produit « Levés bathymétriques », lue le 26/10/2026 : pas d'attribut d'incertitude verticale (seulement horizontale) ; précision verticale 30 cm à 1 m jusqu'à 50 m de fond ; sondes ramenées au zéro hydrographique ; valeur négative = estran</t>
         </is>
       </c>
     </row>

--- a/data/donnees_carte_amidomar.xlsx
+++ b/data/donnees_carte_amidomar.xlsx
@@ -1136,20 +1136,19 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>EMODnet Bathymetry, API depth_sample (grille européenne intégrant les levés du Shom)</t>
+          <t>EMODnet Bathymetry (API depth_sample) pour la valeur — grille européenne qui diffuse les levés du Shom, EDMO 540 ; Shom (WFS « Levés bathymétriques », 4 couches par période) pour le millésime et l'instrument du levé</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>JSON (REST), maille d'environ 115 m</t>
+          <t>JSON (REST) pour la valeur, maille d'environ 115 m ; WFS 2.0.0 GeoJSON filtre INTERSECTS au point pour les levés</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr"/>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Ce qui ne va pas : branchée en v2.6 (25/09/2026) et testée sur l'API réelle, mais le clic complet sur la carte publiée avec l'API réelle reste à vérifier ; la maille d'environ 115 m donne un fond moyen, peu fidèle près des roches et des chenaux. La profondeur n'est pas affichée à l'usager, et elle n'est demandée que si le point est à moins de 100 m d'une AOT.
-Ce qu'il faut : un test en conditions réelles sur la carte publiée ; afficher la profondeur dans la popup au-dessus de la nature du fond, avec la fourchette min/max et le millésime du levé ; trancher la valeur retenue pour le rayon d'évitage (min = prudence anti-collision, max = prudence anti-échouage, avg aujourd'hui).
-Arbitrage du 26/10/2026 : la carte doit porter les deux bornes de la marée (« 13,7 à 19,1 m selon la marée ») et non la seule sonde, sinon deux nombres distants du marnage cohabitent sans lien. En Méditerranée, pas de fourchette ni de mention de marée : la référence y est le niveau moyen.</t>
+          <t>Ce qui ne va pas : branchée dans le popup le 26/10/2026 (v2.29) et testée sur les API réelles, mais le clic sur la carte publiée reste à vérifier ; la maille d'environ 115 m donne un fond moyen, peu fidèle près des roches et des chenaux.
+Ce qu'il faut : vérifier en conditions réelles sur la version publiée que la carte s'affiche avant « Nature du fond », que la Méditerranée n'affiche pas de fourchette, et surtout que le chiffre du champ « Colonne d'eau à marée haute » est bien la borne haute annoncée par la carte.</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">

--- a/data/donnees_carte_amidomar.xlsx
+++ b/data/donnees_carte_amidomar.xlsx
@@ -515,7 +515,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F34"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1110,7 +1110,7 @@
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>GeoJSON, 249 points</t>
+          <t>GeoJSON, 248 points</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr"/>
@@ -1121,7 +1121,8 @@
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>Des positions réelles sont déjà publiées :
+          <t>Rejeu du 29-30/10/2026 (v2.32) : 248 positions fictives, 62 par département (22, 29, 56, 83), sur 8 sites, chacune posée entre 100 et 200 m du trait terre-mer du Shom (distance mesurée sur le service, conservée dans distance_cote_m). Dans le Var, 50 des 62 sont dans les 5 zones de mouillage autorisées de Saint-Tropez. Méthode complète et contrôles : data/SOURCES.md §10. Reste simulé : à remplacer par un export Grist ne contenant que des coordonnées.
+Des positions réelles sont déjà publiées :
 Finistère (DDTM 29) : mouillages individuels sous AOT représentés par un cercle, shapefile, WMS/WFS, extraction ADOC du 28/05/2026, mis à jour le 29/05/2026. Les champs (longueur, statut) ne sont pas documentés sur la page : https://www.data.gouv.fr/datasets/mouillages-individuels-du-finistere-1
 Ille-et-Vilaine (DDTM 35, jeu archivé de 2022) : https://www.data.gouv.fr/datasets/mouillages-individuels-dille-et-vilaine-35
 Autres départements : à demander aux DDTM ; droit de diffusion à confirmer.</t>
@@ -1129,29 +1130,57 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="inlineStr">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Zones de mouillage autorisées (AOT)</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>data/zones-aot.geojson — DDTM du Var / SML-BLO, cartes n°41 et n°42, octobre 2022</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>GeoJSON, 5 polygones</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="n"/>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>Ce qui ne va pas : couverture très partielle — 5 zones sur la seule commune de Saint-Tropez, relevées à la main sur les cartes PDF de la DDTM 83. Ce qu'il faut : faire confirmer ces 5 périmètres par la DDTM 83, puis obtenir les zones des autres communes et des autres départements.</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>Branché le 14/10/2026 (v2.23), affiché en orange #b34000 et interrogé au clic sur le fichier local. Un clic dans une zone ne court-circuite pas le parcours. Pistes : demander à la DDTM 83 un export géographique plutôt qu'un PDF ; vérifier si les autres DDTM publient leurs zones sur GéoIDE ou data.gouv.fr (aucune publication repérée à ce jour, non confirmé). Depuis le 30/10/2026, 50 AOT simulées y sont posées (voir la ligne précédente).</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
         <is>
           <t>Profondeur au point (colonne d'eau à marée haute)</t>
         </is>
       </c>
-      <c r="B21" s="3" t="inlineStr">
+      <c r="B22" s="3" t="inlineStr">
         <is>
           <t>EMODnet Bathymetry (API depth_sample) pour la valeur — grille européenne qui diffuse les levés du Shom, EDMO 540 ; Shom (WFS « Levés bathymétriques », 4 couches par période) pour le millésime et l'instrument du levé</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr">
+      <c r="C22" s="3" t="inlineStr">
         <is>
           <t>JSON (REST) pour la valeur, maille d'environ 115 m ; WFS 2.0.0 GeoJSON filtre INTERSECTS au point pour les levés</t>
         </is>
       </c>
-      <c r="D21" s="3" t="inlineStr"/>
-      <c r="E21" s="3" t="inlineStr">
+      <c r="D22" s="3" t="inlineStr"/>
+      <c r="E22" s="3" t="inlineStr">
         <is>
           <t>Ce qui ne va pas : branchée dans le popup le 26/10/2026 (v2.29) et testée sur les API réelles, mais le clic sur la carte publiée reste à vérifier ; la maille d'environ 115 m donne un fond moyen, peu fidèle près des roches et des chenaux.
 Ce qu'il faut : vérifier en conditions réelles sur la version publiée que la carte s'affiche avant « Nature du fond », que la Méditerranée n'affiche pas de fourchette, et surtout que le chiffre du champ « Colonne d'eau à marée haute » est bien la borne haute annoncée par la carte.</t>
         </is>
       </c>
-      <c r="F21" s="3" t="inlineStr">
+      <c r="F22" s="3" t="inlineStr">
         <is>
           <t>API testée le 25/09/2026 depuis le site publié : CORS accepté, 60 à 370 ms ; Quiberon −12,35 m, Brest −23,6 m, Saint-Malo −1,86 m. Retestée le 15/10/2026 sur 7 sites de mouillage : 28 à 80 ms. https://rest.emodnet-bathymetry.eu/depth_sample?geom=POINT(-2.970485 47.510572)
 La réponse contient déjà min, max, stdev, elementarySurfaces et reference (identifiant du levé) — non lus par la carte aujourd'hui. Les 7 réponses portent organisation_id 540 = Shom (EDMO) : la source de vérité est le Shom, EMODnet en est le véhicule interrogeable. Au large de Saint-Malo la provenance est DTM_GNB_20m, soit le MNT côtier 20 m du golfe normand-breton du Shom lui-même.
@@ -1162,60 +1191,60 @@
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="3" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
         <is>
           <t>Hauteur de marée haute (colonne d'eau à marée haute)</t>
         </is>
       </c>
-      <c r="B22" s="3" t="inlineStr">
+      <c r="B23" s="3" t="inlineStr">
         <is>
           <t>data/ram-ports.json, extrait du Shom, Références Altimétriques Maritimes (WFS RAM_BDD_WLD_WGS84G_WFS:ram_3857)</t>
         </is>
       </c>
-      <c r="C22" s="3" t="inlineStr">
+      <c r="C23" s="3" t="inlineStr">
         <is>
           <t>JSON, 214 ports (métropole)</t>
         </is>
       </c>
-      <c r="D22" s="3" t="n"/>
-      <c r="E22" s="3" t="inlineStr">
+      <c r="D23" s="3" t="n"/>
+      <c r="E23" s="3" t="inlineStr">
         <is>
           <t>Ce qui ne va pas : valeur fixe par port (vives-eaux moyennes, coefficient 95), pas la marée du jour ; port choisi à vol d'oiseau, parfois de l'autre côté d'une pointe ; 15 ports sans valeurs exploitables écartés ; extraction du 25/09/2026 à rafraîchir si le Shom publie une nouvelle édition.
 Ce qu'il faut : garder la table à jour ; pour la marée du jour, un abonnement aux API de prédiction du Shom (payant) avec un petit serveur intermédiaire.</t>
         </is>
       </c>
-      <c r="F22" s="3" t="inlineStr">
+      <c r="F23" s="3" t="inlineStr">
         <is>
           <t>Source ouverte (Licence Ouverte, citer « Shom, 2025 ») : https://www.data.gouv.fr/datasets/references-altimetriques-maritimes — WFS interrogé le 25/09/2026 (446 sites, 229 en métropole, sommes de contrôle notées dans TESTS_FONCTIONNELS.md §5/9quinquies).
 API marée du Shom (payantes, clé) : https://diffusion.shom.fr/api-shom.html</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="3" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
         <is>
           <t>Vent et courant (calcul du rayon d’évitage)</t>
         </is>
       </c>
-      <c r="B23" s="3" t="inlineStr">
+      <c r="B24" s="3" t="inlineStr">
         <is>
           <t>Aucune</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr">
+      <c r="C24" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D23" s="3" t="inlineStr"/>
-      <c r="E23" s="3" t="inlineStr">
+      <c r="D24" s="3" t="inlineStr"/>
+      <c r="E24" s="3" t="inlineStr">
         <is>
           <t>Ce qui ne va pas : le calcul du rayon d'évitage ne tient compte ni du vent ni du courant. La nature du fond, elle, est branchée depuis le 12/10/2026 (ligne ci-dessous) mais n'entre pas dans le calcul : elle sert au conseil d'ancrage.
 Ce qu'il faut : décider si le rayon d'évitage doit intégrer ces paramètres, sachant que le produit resterait indicatif.</t>
         </is>
       </c>
-      <c r="F23" s="3" t="inlineStr">
+      <c r="F24" s="3" t="inlineStr">
         <is>
           <t>Nature du fond : Natures de fond au 1/50 000 (Shom), 47 cartes, shapefile et GML, WMS/WMTS/WFS, gratuit, version 2025 : https://diffusion.shom.fr/donnees/sedimentologie/natures-de-fond.html
 Courants : la page Shom des courants de marée 2D était inaccessible au test, et l'API Shom ne liste ni courants ni vent (marées payantes) : https://diffusion.shom.fr/services-numeriques/api-shom.html
@@ -1224,31 +1253,31 @@
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="10" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="10" t="inlineStr">
         <is>
           <t>Nature du fond au clic (conseil d’ancrage)</t>
         </is>
       </c>
-      <c r="B24" s="10" t="inlineStr">
+      <c r="B25" s="10" t="inlineStr">
         <is>
           <t>SHOM, Natures de fond au 1/50 000, 2025, services INSPIRE</t>
         </is>
       </c>
-      <c r="C24" s="10" t="inlineStr">
+      <c r="C25" s="10" t="inlineStr">
         <is>
           <t>WFS 2.0.0, GeoJSON, filtre INTERSECTS au point ; couche non affichée</t>
         </is>
       </c>
-      <c r="D24" s="10" t="n"/>
-      <c r="E24" s="10" t="inlineStr">
+      <c r="D25" s="10" t="n"/>
+      <c r="E25" s="10" t="inlineStr">
         <is>
           <t>Ce qui ne va pas : la couverture n'est pas nationale. Taux de réponse mesuré le 12/10/2026 sur 30 points en mer tirés au hasard par territoire : Morbihan 100 %, Var 97 %, Finistère 87 %, mais Ille-et-Vilaine 27 % et Côtes-d'Armor 3 %. Le produit synthétise 45 cartes sédimentaires publiées de 1990 à 2023, et les feuilles non publiées laissent des trous.
 Autre limite : c'est une carte SÉDIMENTAIRE, elle ne représente pas les herbiers. Un fond de sable n'exclut pas un herbier.
 Ce qu'il faut : demander au Shom le calendrier de publication des feuilles manquantes, en priorité sur les Côtes-d'Armor (territoire pilote).</t>
         </is>
       </c>
-      <c r="F24" s="10" t="inlineStr">
+      <c r="F25" s="10" t="inlineStr">
         <is>
           <t>Branché le 12/10/2026 (v2.15). Couche NDF_BDD_WLD_WGS84G_WFS:natures_fond_50000, attribut typelem, interrogée en parallèle des zonages. Affichée uniquement quand le mouillage n'est pas interdit.
 Table des 24 libellés établie le 12/10/2026 sans déduction : extraction de la légende officielle (GetLegendGraphic, 33 entrées), puis comparaison, pour chaque code, de la couleur réellement rendue par le WMS au point avec la pastille de légende — 23 correspondances exactes sur 24. Seul NFSFC (un unique polygone en France) est déduit.
@@ -1258,198 +1287,198 @@
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="3" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
         <is>
           <t>Réserves naturelles nationales</t>
         </is>
       </c>
-      <c r="B25" s="3" t="inlineStr">
+      <c r="B26" s="3" t="inlineStr">
         <is>
           <t>Patrinat_RNN (Géoplateforme)</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr">
+      <c r="C26" s="3" t="inlineStr">
         <is>
           <t>Non testé</t>
         </is>
       </c>
-      <c r="D25" s="3" t="inlineStr"/>
-      <c r="E25" s="3" t="inlineStr">
+      <c r="D26" s="3" t="inlineStr"/>
+      <c r="E26" s="3" t="inlineStr">
         <is>
           <t>Ce qui ne va pas : la couche existe mais n'est pas sur la carte, alors que la note la donne « en service ».
 Ce qu'il faut : l'ajouter et la tester.</t>
         </is>
       </c>
-      <c r="F25" s="3" t="inlineStr">
+      <c r="F26" s="3" t="inlineStr">
         <is>
           <t>Couche patrinat_rnn confirmée dans le document de capacités WFS de la Géoplateforme (21/09/2026) : https://data.geopf.fr/wfs?REQUEST=GetCapabilities&amp;SERVICE=WFS&amp;VERSION=2.0.0</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>Arrêtés de protection de biotope (APB)</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>IGN / INPN, Patrinat_APB</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
         <is>
           <t>WMTS, tuiles PNG raster</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>données fonctionnelles</t>
         </is>
       </c>
-      <c r="E26" s="2" t="n"/>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="E27" s="2" t="n"/>
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>Affichage : couche patrinat_apb confirmée en WFS et en WMTS le 21/09/2026 ; polygones vus au Morbihan (zoom 11), couleur de légende orange alignée sur les tuiles.
 Au clic (v2.0, 22/09/2026) : couche patrinat_apb:apb, champ nom_site, filtre INTERSECTS. Testé en direct sur l'APB « Ile Dumet et ses abords » (centre du polygone, pas un sommet) : nom renvoyé en ~480 ms. Traité comme une interdiction bloquante, prioritaire sur Natura 2000/ZNIEFF (popup rouge, pas de coordonnées), vérifiée avant tout affichage (délai 4 s, défaut non bloquant). Reste à tester : un clic réel dans un APB sur la carte publiée.</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="3" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
         <is>
           <t>Autres zonages (Ramsar, RNR, Conservatoire du littoral)</t>
         </is>
       </c>
-      <c r="B27" s="3" t="inlineStr">
+      <c r="B28" s="3" t="inlineStr">
         <is>
           <t>Patrinat_RAMSAR, Patrinat_RNR, CONSERVATOIRE_LITTORAL.PERIMETRES</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr">
+      <c r="C28" s="3" t="inlineStr">
         <is>
           <t>Non testé</t>
         </is>
       </c>
-      <c r="D27" s="3" t="inlineStr"/>
-      <c r="E27" s="3" t="inlineStr">
+      <c r="D28" s="3" t="inlineStr"/>
+      <c r="E28" s="3" t="inlineStr">
         <is>
           <t>Ce qui ne va pas : couches existantes mais absentes de la carte.
 Ce qu'il faut : décider si le besoin métier justifie de les ajouter, puis vérifier le rendu.</t>
         </is>
       </c>
-      <c r="F27" s="3" t="inlineStr">
+      <c r="F28" s="3" t="inlineStr">
         <is>
           <t>WFS Géoplateforme : patrinat_ramsar et CONSERVATOIRE_LITTORAL.PERIMETRES sont listées ; patrinat_rnr y figure aussi (noms confirmés le 21/09/2026 ; requêtes de données non testées) : https://data.geopf.fr/wfs?REQUEST=GetCapabilities&amp;SERVICE=WFS&amp;VERSION=2.0.0
 Espaces protégés du Conservatoire du littoral (titre repéré, non ouvert) : https://www.data.gouv.fr/datasets/site-des-espaces-proteges-du-conservatoire-du-littoral</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="3" t="inlineStr">
+    <row r="29" ht="150" customHeight="1">
+      <c r="A29" s="3" t="inlineStr">
         <is>
           <t>Zones de baignade et zones réglementaires</t>
         </is>
       </c>
-      <c r="B28" s="3" t="inlineStr">
+      <c r="B29" s="3" t="inlineStr">
         <is>
           <t>Aucune</t>
         </is>
       </c>
-      <c r="C28" s="3" t="inlineStr">
+      <c r="C29" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D28" s="3" t="n"/>
-      <c r="E28" s="3" t="inlineStr">
+      <c r="D29" s="3" t="n"/>
+      <c r="E29" s="3" t="inlineStr">
         <is>
           <t>Ce qui ne va pas : ligne « à venir » dans la légende, grisée et non sélectionnable. Aucune source n'est identifiée pour représenter ces zones ni les reconnaître au clic.
 Ce qu'il faut : identifier une source pour chacune des deux.</t>
         </is>
       </c>
-      <c r="F28" s="3" t="inlineStr">
+      <c r="F29" s="3" t="inlineStr">
         <is>
           <t>Aucune source confirmée. Pistes non vérifiées : données de baignade publiées par les communes ou les ARS, arrêtés préfectoraux à demander aux DDTM/DM.</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="150" customHeight="1">
-      <c r="A29" s="9" t="inlineStr">
+    <row r="30" ht="190" customHeight="1">
+      <c r="A30" s="9" t="inlineStr">
         <is>
           <t>Rattachement départemental au clic (quelle DDTM ?)</t>
         </is>
       </c>
-      <c r="B29" s="9" t="inlineStr">
+      <c r="B30" s="9" t="inlineStr">
         <is>
           <t>SHOM-IGN, LIMTM 2021, services INSPIRE — attribut numdep de la couche limite_terre_mer_france_metropolitaine_polygones</t>
         </is>
       </c>
-      <c r="C29" s="9" t="inlineStr">
+      <c r="C30" s="9" t="inlineStr">
         <is>
           <t>WFS 2.0.0, GeoJSON, filtre DWITHIN à rayons progressifs (1, 2, 5, 10 km)</t>
         </is>
       </c>
-      <c r="D29" s="9" t="inlineStr">
+      <c r="D30" s="9" t="inlineStr">
         <is>
           <t>données fonctionnelles</t>
         </is>
       </c>
-      <c r="E29" s="9" t="inlineStr"/>
-      <c r="F29" s="9" t="inlineStr">
+      <c r="E30" s="9" t="inlineStr"/>
+      <c r="F30" s="9" t="inlineStr">
         <is>
           <t>Branché le 14/10/2026 (v2.22), sans nouvelle source : la couche était déjà interrogée depuis la v2.14 et renvoyait déjà numdep. Calibrage vérifié en réel le 14/10/2026 sur 6 points (rade de Brest 29, golfe du Morbihan 56, rade de Toulon 83, Les Sept-Îles 22, baie de Saint-Brieuc 22) : réponse univoque à chaque fois. LIMITE À CONNAÎTRE : la couche porte des surfaces TERRESTRES, le département est donc celui de la côte la plus proche, jamais celui du point cliqué — c'est une inférence, et aucune limite départementale ne s'étend en mer dans ce jeu. Piste pour lever cette limite : demander au Shom (Eric Le Guen, équipe zones et limites maritimes) s'il existe un référentiel de limites administratives EN MER diffusable.</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="190" customHeight="1">
-      <c r="A30" s="11" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="11" t="inlineStr">
         <is>
           <t>Messages d'orientation par DDTM (règles locales)</t>
         </is>
       </c>
-      <c r="B30" s="11" t="inlineStr">
+      <c r="B31" s="11" t="inlineStr">
         <is>
           <t>data/ddtm-messages.json — rédigé par l'équipe, en attendant l'interface instructeur Grist</t>
         </is>
       </c>
-      <c r="C30" s="11" t="inlineStr">
+      <c r="C31" s="11" t="inlineStr">
         <is>
           <t>JSON, texte brut échappé à l'affichage, 2 fiches (22 et 83). Le 83 porte deux jeux de textes : l'état par défaut et l'état « emplacement dans une zone autorisée » (champs *_zone, v2.24)</t>
         </is>
       </c>
-      <c r="D30" s="11" t="inlineStr"/>
-      <c r="E30" s="11" t="inlineStr">
+      <c r="D31" s="11" t="inlineStr"/>
+      <c r="E31" s="11" t="inlineStr">
         <is>
           <t>Ce qui ne va pas : la liste des zones du Var est partielle. Les 5 zones reçues de la DDTM 83 (cartes PDF n°41 Les Canebiers et n°42 La Bouillabaisse, octobre 2022) sont toutes sur la commune de Saint-Tropez, alors que la DDTM 83 couvre toute la façade varoise. Le texte de la carte l'annonce et le drapeau brouillon reste posé, mais il faut obtenir les zones des autres communes (Hyères, Giens, Porquerolles, Cavalaire, Le Lavandou, Bandol...). Le 29 et le 56 n'ont pas de message, ce qui est normal à ce jour.</t>
         </is>
       </c>
-      <c r="F30" s="11" t="inlineStr">
+      <c r="F31" s="11" t="inlineStr">
         <is>
           <t>Fichier PROVISOIRE par conception : il sera régénéré depuis la table DDTM de Grist quand l'interface instructeur permettra aux agents de gérer leurs bandeaux par périmètre en autonomie. Ses noms de champs sont déjà ceux prévus pour cette table. PISTE NON ENGAGÉE : les deux cartes PDF donnent les 4 sommets GPS de chaque zone (degrés-minutes décimales). Les convertir en polygones GeoJSON permettrait de répondre directement à la question de l'usager (« mon emplacement est-il dans une zone autorisée ? ») au lieu de lui faire lire une liste de noms, et d'afficher les zones sur la carte comme les ZMEL. Secours hors ligne volontairement vide.</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="5" t="n"/>
-    </row>
     <row r="32">
-      <c r="A32" s="5" t="inlineStr">
-        <is>
-          <t>Légende : vert = données fonctionnelles ; jaune = données simulées ; sans couleur = à compléter.</t>
-        </is>
-      </c>
+      <c r="A32" s="5" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>Méthode (21/09/2026) : les fiches de jeux de données ont été ouvertes et lues ; les services WMS/WFS et les fichiers n'ont pas été interrogés ni téléchargés. « Titre repéré, non ouvert » = trouvé par recherche seulement.</t>
+          <t>Légende : vert = données fonctionnelles ; jaune = données simulées ; sans couleur = à compléter.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>Méthode (21/09/2026) : les fiches de jeux de données ont été ouvertes et lues ; les services WMS/WFS et les fichiers n'ont pas été interrogés ni téléchargés. « Titre repéré, non ouvert » = trouvé par recherche seulement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
         <is>
           <t>Le document de capacités WFS et WMTS de la Géoplateforme a été interrogé dans un navigateur le 21/09/2026 : les noms de couches patrinat_* cités ici y figurent. Aucune requête de données (GetFeature) n'a encore été testée.</t>
         </is>
